--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_gmprob.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_gmprob.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -1027,364 +1028,364 @@
         <v>23</v>
       </c>
       <c r="D2" s="0">
-        <v>0.43665054440498352</v>
+        <v>0.29016366600990296</v>
       </c>
       <c r="E2" s="0">
-        <v>0.39848268032073975</v>
+        <v>0.27916848659515381</v>
       </c>
       <c r="F2" s="0">
-        <v>0.42352941632270813</v>
+        <v>0.28429833054542542</v>
       </c>
       <c r="G2" s="0">
-        <v>0.39555367827415466</v>
+        <v>0.28285950422286987</v>
       </c>
       <c r="H2" s="0">
-        <v>0.39441061019897461</v>
+        <v>0.26430049538612366</v>
       </c>
       <c r="I2" s="0">
-        <v>0.42530342936515808</v>
+        <v>0.2919594943523407</v>
       </c>
       <c r="J2" s="0">
-        <v>0.39190894365310669</v>
+        <v>0.26853969693183899</v>
       </c>
       <c r="K2" s="0">
-        <v>0.40280985832214355</v>
+        <v>0.28170067071914673</v>
       </c>
       <c r="L2" s="0">
-        <v>0.42055708169937134</v>
+        <v>0.2813628613948822</v>
       </c>
       <c r="M2" s="0">
-        <v>0.41070970892906189</v>
+        <v>0.27894285321235657</v>
       </c>
       <c r="N2" s="0">
-        <v>0.48023957014083862</v>
+        <v>0.36655968427658081</v>
       </c>
       <c r="O2" s="0">
-        <v>0.44156369566917419</v>
+        <v>0.33463796973228455</v>
       </c>
       <c r="P2" s="0">
-        <v>0.39113956689834595</v>
+        <v>0.2438025027513504</v>
       </c>
       <c r="Q2" s="0">
-        <v>0.40831482410430908</v>
+        <v>0.29120790958404541</v>
       </c>
       <c r="R2" s="0">
-        <v>0.44239705801010132</v>
+        <v>0.31407153606414795</v>
       </c>
       <c r="S2" s="0">
-        <v>0.4758371114730835</v>
+        <v>0.33309257030487061</v>
       </c>
       <c r="T2" s="0">
-        <v>0.36677321791648865</v>
+        <v>0.25253614783287048</v>
       </c>
       <c r="U2" s="0">
-        <v>0.37646466493606567</v>
+        <v>0.26104816794395447</v>
       </c>
       <c r="V2" s="0">
-        <v>0.45144137740135193</v>
+        <v>0.31130304932594299</v>
       </c>
       <c r="W2" s="0">
-        <v>0.41558030247688293</v>
+        <v>0.28344136476516724</v>
       </c>
       <c r="X2" s="0">
-        <v>0.311717689037323</v>
+        <v>0.41186192631721497</v>
       </c>
       <c r="Y2" s="0">
-        <v>0.32077980041503906</v>
+        <v>0.34527021646499634</v>
       </c>
       <c r="Z2" s="0">
-        <v>0.36748367547988892</v>
+        <v>0.38570749759674072</v>
       </c>
       <c r="AA2" s="0">
-        <v>0.29885485768318176</v>
+        <v>0.36873027682304382</v>
       </c>
       <c r="AB2" s="0">
-        <v>0.33441904187202454</v>
+        <v>0.26360547542572022</v>
       </c>
       <c r="AC2" s="0">
-        <v>0.31630980968475342</v>
+        <v>0.41067472100257874</v>
       </c>
       <c r="AD2" s="0">
-        <v>0.28976494073867798</v>
+        <v>0.3348885178565979</v>
       </c>
       <c r="AE2" s="0">
-        <v>0.28659921884536743</v>
+        <v>0.31387144327163696</v>
       </c>
       <c r="AF2" s="0">
-        <v>0.30310580134391785</v>
+        <v>0.32428351044654846</v>
       </c>
       <c r="AG2" s="0">
-        <v>0.29952123761177063</v>
+        <v>0.33526727557182312</v>
       </c>
       <c r="AH2" s="0">
-        <v>0.40896636247634888</v>
+        <v>0.44509518146514893</v>
       </c>
       <c r="AI2" s="0">
-        <v>0.36531317234039307</v>
+        <v>0.37787219882011414</v>
       </c>
       <c r="AJ2" s="0">
-        <v>0.33491876721382141</v>
+        <v>0.3677351176738739</v>
       </c>
       <c r="AK2" s="0">
-        <v>0.30736497044563293</v>
+        <v>0.33880198001861572</v>
       </c>
       <c r="AL2" s="0">
-        <v>0.31569001078605652</v>
+        <v>0.3847694993019104</v>
       </c>
       <c r="AM2" s="0">
-        <v>0.29604071378707886</v>
+        <v>0.34365150332450867</v>
       </c>
       <c r="AN2" s="0">
-        <v>0.35128700733184814</v>
+        <v>0.33490398526191712</v>
       </c>
       <c r="AO2" s="0">
-        <v>0.32132387161254883</v>
+        <v>0.37573933601379395</v>
       </c>
       <c r="AP2" s="0">
-        <v>0.29037976264953613</v>
+        <v>0.29771134257316589</v>
       </c>
       <c r="AQ2" s="0">
-        <v>0.27638539671897888</v>
+        <v>0.30406886339187622</v>
       </c>
       <c r="AR2" s="0">
-        <v>0.26685762405395508</v>
+        <v>0.33126658201217651</v>
       </c>
       <c r="AS2" s="0">
-        <v>0.32802078127861023</v>
+        <v>0.3373706042766571</v>
       </c>
       <c r="AT2" s="0">
-        <v>0.40348511934280396</v>
+        <v>0.37091365456581116</v>
       </c>
       <c r="AU2" s="0">
-        <v>0.34979185461997986</v>
+        <v>0.38462081551551819</v>
       </c>
       <c r="AV2" s="0">
-        <v>0.36357909440994263</v>
+        <v>0.30649116635322571</v>
       </c>
       <c r="AW2" s="0">
-        <v>0.36230319738388062</v>
+        <v>0.31681150197982788</v>
       </c>
       <c r="AX2" s="0">
-        <v>0.34831610321998596</v>
+        <v>0.41298514604568481</v>
       </c>
       <c r="AY2" s="0">
-        <v>0.3110562264919281</v>
+        <v>0.42029285430908203</v>
       </c>
       <c r="AZ2" s="0">
-        <v>0.28396138548851013</v>
+        <v>0.36557430028915405</v>
       </c>
       <c r="BA2" s="0">
-        <v>0.31689652800559998</v>
+        <v>0.37121602892875671</v>
       </c>
       <c r="BB2" s="0">
-        <v>0.31894955039024353</v>
+        <v>0.34653362631797791</v>
       </c>
       <c r="BC2" s="0">
-        <v>0.36450406908988953</v>
+        <v>0.34273761510848999</v>
       </c>
       <c r="BD2" s="0">
-        <v>0.30768498778343201</v>
+        <v>0.28832989931106567</v>
       </c>
       <c r="BE2" s="0">
-        <v>0.3135790228843689</v>
+        <v>0.34793934226036072</v>
       </c>
       <c r="BF2" s="0">
-        <v>0.36606928706169128</v>
+        <v>0.37380948662757874</v>
       </c>
       <c r="BG2" s="0">
-        <v>0.36131718754768372</v>
+        <v>0.38654467463493347</v>
       </c>
       <c r="BH2" s="0">
-        <v>0.38729032874107361</v>
+        <v>0.33366501331329346</v>
       </c>
       <c r="BI2" s="0">
-        <v>0.31309682130813599</v>
+        <v>0.36323347687721253</v>
       </c>
       <c r="BJ2" s="0">
-        <v>0.35200780630111694</v>
+        <v>0.35469838976860046</v>
       </c>
       <c r="BK2" s="0">
-        <v>0.33917519450187683</v>
+        <v>0.32658553123474121</v>
       </c>
       <c r="BL2" s="0">
-        <v>0.31332173943519592</v>
+        <v>0.34159091114997864</v>
       </c>
       <c r="BM2" s="0">
-        <v>0.40755957365036011</v>
+        <v>0.35071888566017151</v>
       </c>
       <c r="BN2" s="0">
-        <v>0.37307083606719971</v>
+        <v>0.32097399234771729</v>
       </c>
       <c r="BO2" s="0">
-        <v>0.36294889450073242</v>
+        <v>0.33989855647087097</v>
       </c>
       <c r="BP2" s="0">
-        <v>0.30841216444969177</v>
+        <v>0.3538358211517334</v>
       </c>
       <c r="BQ2" s="0">
-        <v>0.36478534340858459</v>
+        <v>0.38442239165306091</v>
       </c>
       <c r="BR2" s="0">
-        <v>0.33282139897346497</v>
+        <v>0.3542921245098114</v>
       </c>
       <c r="BS2" s="0">
-        <v>0.35094919800758362</v>
+        <v>0.41790792346000671</v>
       </c>
       <c r="BT2" s="0">
-        <v>0.34421685338020325</v>
+        <v>0.33732542395591736</v>
       </c>
       <c r="BU2" s="0">
-        <v>0.3672630786895752</v>
+        <v>0.38512489199638367</v>
       </c>
       <c r="BV2" s="0">
-        <v>0.34774896502494812</v>
+        <v>0.35495361685752869</v>
       </c>
       <c r="BW2" s="0">
-        <v>0.31585785746574402</v>
+        <v>0.4092387855052948</v>
       </c>
       <c r="BX2" s="0">
-        <v>0.35199165344238281</v>
+        <v>0.30462676286697388</v>
       </c>
       <c r="BY2" s="0">
-        <v>0.37320193648338318</v>
+        <v>0.39890235662460327</v>
       </c>
       <c r="BZ2" s="0">
-        <v>0.37131780385971069</v>
+        <v>0.36954346299171448</v>
       </c>
       <c r="CA2" s="0">
-        <v>0.26925477385520935</v>
+        <v>0.37903887033462524</v>
       </c>
       <c r="CB2" s="0">
-        <v>0.42372933030128479</v>
+        <v>0.39544972777366638</v>
       </c>
       <c r="CC2" s="0">
-        <v>0.34567102789878845</v>
+        <v>0.36920878291130066</v>
       </c>
       <c r="CD2" s="0">
-        <v>0.33789193630218506</v>
+        <v>0.36480203270912171</v>
       </c>
       <c r="CE2" s="0">
-        <v>0.3296782374382019</v>
+        <v>0.3752555251121521</v>
       </c>
       <c r="CF2" s="0">
-        <v>0.34497243165969849</v>
+        <v>0.35164034366607666</v>
       </c>
       <c r="CG2" s="0">
-        <v>0.36794760823249817</v>
+        <v>0.40216481685638428</v>
       </c>
       <c r="CH2" s="0">
-        <v>0.28595349192619324</v>
+        <v>0.31942099332809448</v>
       </c>
       <c r="CI2" s="0">
-        <v>0.25658920407295227</v>
+        <v>0.27908676862716675</v>
       </c>
       <c r="CJ2" s="0">
-        <v>0.37963324785232544</v>
+        <v>0.38477718830108643</v>
       </c>
       <c r="CK2" s="0">
-        <v>0.3958551287651062</v>
+        <v>0.39831551909446716</v>
       </c>
       <c r="CL2" s="0">
-        <v>0.34061625599861145</v>
+        <v>0.35412698984146118</v>
       </c>
       <c r="CM2" s="0">
-        <v>0.33612239360809326</v>
+        <v>0.30937331914901733</v>
       </c>
       <c r="CN2" s="0">
-        <v>0.38295513391494751</v>
+        <v>0.36715105175971985</v>
       </c>
       <c r="CO2" s="0">
-        <v>0.35802698135375977</v>
+        <v>0.39233598113059998</v>
       </c>
       <c r="CP2" s="0">
-        <v>0.36511716246604919</v>
+        <v>0.36665841937065125</v>
       </c>
       <c r="CQ2" s="0">
-        <v>0.36584794521331787</v>
+        <v>0.33875274658203125</v>
       </c>
       <c r="CR2" s="0">
-        <v>0.3804967999458313</v>
+        <v>0.41472887992858887</v>
       </c>
       <c r="CS2" s="0">
-        <v>0.32779154181480408</v>
+        <v>0.44004473090171814</v>
       </c>
       <c r="CT2" s="0">
-        <v>0.34085670113563538</v>
+        <v>0.43164864182472229</v>
       </c>
       <c r="CU2" s="0">
-        <v>0.32061865925788879</v>
+        <v>0.34550198912620544</v>
       </c>
       <c r="CV2" s="0">
-        <v>0.32272028923034668</v>
+        <v>0.36488378047943115</v>
       </c>
       <c r="CW2" s="0">
-        <v>0.38412916660308838</v>
+        <v>0.32326039671897888</v>
       </c>
       <c r="CX2" s="0">
-        <v>0.28261637687683105</v>
+        <v>0.32908535003662109</v>
       </c>
       <c r="CY2" s="0">
-        <v>0.28742074966430664</v>
+        <v>0.28495413064956665</v>
       </c>
       <c r="CZ2" s="0">
-        <v>0.33375394344329834</v>
+        <v>0.36110725998878479</v>
       </c>
       <c r="DA2" s="0">
-        <v>0.34723678231239319</v>
+        <v>0.33053895831108093</v>
       </c>
       <c r="DB2" s="0">
-        <v>0.3831028938293457</v>
+        <v>0.36518138647079468</v>
       </c>
       <c r="DC2" s="0">
-        <v>0.32359522581100464</v>
+        <v>0.33434474468231201</v>
       </c>
       <c r="DD2" s="0">
-        <v>0.22950999438762665</v>
+        <v>0.26374232769012451</v>
       </c>
       <c r="DE2" s="0">
-        <v>0.27373617887496948</v>
+        <v>0.25298532843589783</v>
       </c>
       <c r="DF2" s="0">
-        <v>0.32522639632225037</v>
+        <v>0.33392196893692017</v>
       </c>
       <c r="DG2" s="0">
-        <v>0.32881534099578857</v>
+        <v>0.41168355941772461</v>
       </c>
       <c r="DH2" s="0">
-        <v>0.32998001575469971</v>
+        <v>0.42080250382423401</v>
       </c>
       <c r="DI2" s="0">
-        <v>0.3776279091835022</v>
+        <v>0.36567372083663941</v>
       </c>
       <c r="DJ2" s="0">
-        <v>0.32207918167114258</v>
+        <v>0.31949114799499512</v>
       </c>
       <c r="DK2" s="0">
-        <v>0.31380593776702881</v>
+        <v>0.34519305825233459</v>
       </c>
       <c r="DL2" s="0">
-        <v>0.25239166617393494</v>
+        <v>0.26484200358390808</v>
       </c>
       <c r="DM2" s="0">
-        <v>0.34626632928848267</v>
+        <v>0.37737792730331421</v>
       </c>
       <c r="DN2" s="0">
-        <v>0.42930847406387329</v>
+        <v>0.42284262180328369</v>
       </c>
       <c r="DO2" s="0">
-        <v>0.36739268898963928</v>
+        <v>0.4008183479309082</v>
       </c>
       <c r="DP2" s="0">
-        <v>0.34594818949699402</v>
+        <v>0.36745208501815796</v>
       </c>
       <c r="DQ2" s="0">
-        <v>0.30730682611465454</v>
+        <v>0.34891358017921448</v>
       </c>
       <c r="DR2" s="0">
-        <v>0.35293185710906982</v>
+        <v>0.31727048754692078</v>
       </c>
       <c r="DS2" s="0">
-        <v>0.31210076808929443</v>
+        <v>0.34924390912055969</v>
       </c>
     </row>
     <row r="3">
@@ -1398,364 +1399,364 @@
         <v>24</v>
       </c>
       <c r="D3" s="0">
-        <v>0.31633672118186951</v>
+        <v>0.36734876036643982</v>
       </c>
       <c r="E3" s="0">
-        <v>0.31087124347686768</v>
+        <v>0.35644629597663879</v>
       </c>
       <c r="F3" s="0">
-        <v>0.30755341053009033</v>
+        <v>0.36748012900352478</v>
       </c>
       <c r="G3" s="0">
-        <v>0.29670688509941101</v>
+        <v>0.35987678170204163</v>
       </c>
       <c r="H3" s="0">
-        <v>0.30072417855262756</v>
+        <v>0.36882492899894714</v>
       </c>
       <c r="I3" s="0">
-        <v>0.30187612771987915</v>
+        <v>0.36186185479164124</v>
       </c>
       <c r="J3" s="0">
-        <v>0.28993740677833557</v>
+        <v>0.32568961381912231</v>
       </c>
       <c r="K3" s="0">
-        <v>0.30407238006591797</v>
+        <v>0.33912214636802673</v>
       </c>
       <c r="L3" s="0">
-        <v>0.30462443828582764</v>
+        <v>0.37376478314399719</v>
       </c>
       <c r="M3" s="0">
-        <v>0.29343670606613159</v>
+        <v>0.34642601013183594</v>
       </c>
       <c r="N3" s="0">
-        <v>0.39810702204704285</v>
+        <v>0.43791937828063965</v>
       </c>
       <c r="O3" s="0">
-        <v>0.33475804328918457</v>
+        <v>0.40621942281723022</v>
       </c>
       <c r="P3" s="0">
-        <v>0.26508307456970215</v>
+        <v>0.33956041932106018</v>
       </c>
       <c r="Q3" s="0">
-        <v>0.29950979351997375</v>
+        <v>0.36083132028579712</v>
       </c>
       <c r="R3" s="0">
-        <v>0.31806820631027222</v>
+        <v>0.39822828769683838</v>
       </c>
       <c r="S3" s="0">
-        <v>0.35313680768013</v>
+        <v>0.41538974642753601</v>
       </c>
       <c r="T3" s="0">
-        <v>0.24954454600811005</v>
+        <v>0.31696397066116333</v>
       </c>
       <c r="U3" s="0">
-        <v>0.27852198481559753</v>
+        <v>0.33090734481811524</v>
       </c>
       <c r="V3" s="0">
-        <v>0.32855528593063354</v>
+        <v>0.38006839156150818</v>
       </c>
       <c r="W3" s="0">
-        <v>0.32691672444343567</v>
+        <v>0.37349888682365417</v>
       </c>
       <c r="X3" s="0">
-        <v>0.34875470399856567</v>
+        <v>0.3492073118686676</v>
       </c>
       <c r="Y3" s="0">
-        <v>0.2825164794921875</v>
+        <v>0.31036844849586487</v>
       </c>
       <c r="Z3" s="0">
-        <v>0.32764405012130737</v>
+        <v>0.28300854563713074</v>
       </c>
       <c r="AA3" s="0">
-        <v>0.32468676567077637</v>
+        <v>0.27066159248352051</v>
       </c>
       <c r="AB3" s="0">
-        <v>0.34550625085830688</v>
+        <v>0.27890056371688843</v>
       </c>
       <c r="AC3" s="0">
-        <v>0.37881383299827576</v>
+        <v>0.30909061431884766</v>
       </c>
       <c r="AD3" s="0">
-        <v>0.28660020232200623</v>
+        <v>0.26702272891998291</v>
       </c>
       <c r="AE3" s="0">
-        <v>0.23290207982063293</v>
+        <v>0.26627615094184876</v>
       </c>
       <c r="AF3" s="0">
-        <v>0.31628760695457458</v>
+        <v>0.31614792346954346</v>
       </c>
       <c r="AG3" s="0">
-        <v>0.32906153798103333</v>
+        <v>0.3006604015827179</v>
       </c>
       <c r="AH3" s="0">
-        <v>0.35260632634162903</v>
+        <v>0.36583244800567627</v>
       </c>
       <c r="AI3" s="0">
-        <v>0.29755771160125732</v>
+        <v>0.27575033903121948</v>
       </c>
       <c r="AJ3" s="0">
-        <v>0.30454474687576294</v>
+        <v>0.32513144612312317</v>
       </c>
       <c r="AK3" s="0">
-        <v>0.31005069613456726</v>
+        <v>0.33133998513221741</v>
       </c>
       <c r="AL3" s="0">
-        <v>0.30998703837394714</v>
+        <v>0.29276132583618164</v>
       </c>
       <c r="AM3" s="0">
-        <v>0.29545697569847107</v>
+        <v>0.25708094239234924</v>
       </c>
       <c r="AN3" s="0">
-        <v>0.35529646277427673</v>
+        <v>0.38516542315483093</v>
       </c>
       <c r="AO3" s="0">
-        <v>0.31734076142311096</v>
+        <v>0.36062899231910706</v>
       </c>
       <c r="AP3" s="0">
-        <v>0.30527794361114502</v>
+        <v>0.34592366218566895</v>
       </c>
       <c r="AQ3" s="0">
-        <v>0.29064077138900757</v>
+        <v>0.31210300326347351</v>
       </c>
       <c r="AR3" s="0">
-        <v>0.30080604553222656</v>
+        <v>0.32448431849479675</v>
       </c>
       <c r="AS3" s="0">
-        <v>0.29830369353294373</v>
+        <v>0.32179099321365357</v>
       </c>
       <c r="AT3" s="0">
-        <v>0.35165798664093018</v>
+        <v>0.27204123139381409</v>
       </c>
       <c r="AU3" s="0">
-        <v>0.35608184337615967</v>
+        <v>0.38498640060424805</v>
       </c>
       <c r="AV3" s="0">
-        <v>0.38726004958152771</v>
+        <v>0.25468140840530396</v>
       </c>
       <c r="AW3" s="0">
-        <v>0.33922049403190613</v>
+        <v>0.26576462388038635</v>
       </c>
       <c r="AX3" s="0">
-        <v>0.32492020726203918</v>
+        <v>0.36286959052085876</v>
       </c>
       <c r="AY3" s="0">
-        <v>0.36919230222702026</v>
+        <v>0.29638290405273438</v>
       </c>
       <c r="AZ3" s="0">
-        <v>0.27468675374984741</v>
+        <v>0.34600850939750671</v>
       </c>
       <c r="BA3" s="0">
-        <v>0.3475690484046936</v>
+        <v>0.29807877540588379</v>
       </c>
       <c r="BB3" s="0">
-        <v>0.3492794930934906</v>
+        <v>0.29680705070495605</v>
       </c>
       <c r="BC3" s="0">
-        <v>0.32237562537193298</v>
+        <v>0.31998589634895325</v>
       </c>
       <c r="BD3" s="0">
-        <v>0.29681268334388733</v>
+        <v>0.26150685548782349</v>
       </c>
       <c r="BE3" s="0">
-        <v>0.34093180298805237</v>
+        <v>0.37456321716308594</v>
       </c>
       <c r="BF3" s="0">
-        <v>0.3498530387878418</v>
+        <v>0.29280802607536316</v>
       </c>
       <c r="BG3" s="0">
-        <v>0.33417138457298279</v>
+        <v>0.30095705389976501</v>
       </c>
       <c r="BH3" s="0">
-        <v>0.3992370069026947</v>
+        <v>0.37049201130867004</v>
       </c>
       <c r="BI3" s="0">
-        <v>0.34678390622138977</v>
+        <v>0.35094848275184631</v>
       </c>
       <c r="BJ3" s="0">
-        <v>0.32505938410758972</v>
+        <v>0.27993541955947876</v>
       </c>
       <c r="BK3" s="0">
-        <v>0.29045203328132629</v>
+        <v>0.3159787654876709</v>
       </c>
       <c r="BL3" s="0">
-        <v>0.37421175837516785</v>
+        <v>0.33347472548484802</v>
       </c>
       <c r="BM3" s="0">
-        <v>0.30492940545082092</v>
+        <v>0.27550962567329407</v>
       </c>
       <c r="BN3" s="0">
-        <v>0.29526734352111816</v>
+        <v>0.33123105764389038</v>
       </c>
       <c r="BO3" s="0">
-        <v>0.33951598405838013</v>
+        <v>0.32949835062026978</v>
       </c>
       <c r="BP3" s="0">
-        <v>0.38274329900741577</v>
+        <v>0.28941076993942261</v>
       </c>
       <c r="BQ3" s="0">
-        <v>0.37928122282028198</v>
+        <v>0.28015154600143433</v>
       </c>
       <c r="BR3" s="0">
-        <v>0.30525606870651245</v>
+        <v>0.35142523050308228</v>
       </c>
       <c r="BS3" s="0">
-        <v>0.33988270163536072</v>
+        <v>0.30325266718864441</v>
       </c>
       <c r="BT3" s="0">
-        <v>0.28100255131721497</v>
+        <v>0.30538308620452881</v>
       </c>
       <c r="BU3" s="0">
-        <v>0.34488403797149658</v>
+        <v>0.35393396019935608</v>
       </c>
       <c r="BV3" s="0">
-        <v>0.36472022533416748</v>
+        <v>0.33482164144515991</v>
       </c>
       <c r="BW3" s="0">
-        <v>0.33902660012245178</v>
+        <v>0.29783213138580322</v>
       </c>
       <c r="BX3" s="0">
-        <v>0.31737855076789856</v>
+        <v>0.34879651665687561</v>
       </c>
       <c r="BY3" s="0">
-        <v>0.3624933660030365</v>
+        <v>0.35357180237770081</v>
       </c>
       <c r="BZ3" s="0">
-        <v>0.40429648756980896</v>
+        <v>0.3381841778755188</v>
       </c>
       <c r="CA3" s="0">
-        <v>0.32736107707023621</v>
+        <v>0.34952104091644287</v>
       </c>
       <c r="CB3" s="0">
-        <v>0.37029168009757996</v>
+        <v>0.39719504117965698</v>
       </c>
       <c r="CC3" s="0">
-        <v>0.35704201459884644</v>
+        <v>0.32224166393280029</v>
       </c>
       <c r="CD3" s="0">
-        <v>0.30271217226982117</v>
+        <v>0.32834944128990173</v>
       </c>
       <c r="CE3" s="0">
-        <v>0.29572185873985291</v>
+        <v>0.24297696352005005</v>
       </c>
       <c r="CF3" s="0">
-        <v>0.35968935489654541</v>
+        <v>0.382550448179245</v>
       </c>
       <c r="CG3" s="0">
-        <v>0.33008602261543274</v>
+        <v>0.33273237943649292</v>
       </c>
       <c r="CH3" s="0">
-        <v>0.26106199622154236</v>
+        <v>0.23619230091571808</v>
       </c>
       <c r="CI3" s="0">
-        <v>0.29173570871353149</v>
+        <v>0.23649068176746368</v>
       </c>
       <c r="CJ3" s="0">
-        <v>0.2851739227771759</v>
+        <v>0.32367798686027527</v>
       </c>
       <c r="CK3" s="0">
-        <v>0.3142126202583313</v>
+        <v>0.38536050915718079</v>
       </c>
       <c r="CL3" s="0">
-        <v>0.32548269629478455</v>
+        <v>0.32761502265930176</v>
       </c>
       <c r="CM3" s="0">
-        <v>0.28370240330696106</v>
+        <v>0.31131356954574585</v>
       </c>
       <c r="CN3" s="0">
-        <v>0.33197012543678284</v>
+        <v>0.32845157384872437</v>
       </c>
       <c r="CO3" s="0">
-        <v>0.44081804156303406</v>
+        <v>0.31629407405853272</v>
       </c>
       <c r="CP3" s="0">
-        <v>0.30138340592384338</v>
+        <v>0.34487885236740112</v>
       </c>
       <c r="CQ3" s="0">
-        <v>0.3010827898979187</v>
+        <v>0.33052584528923035</v>
       </c>
       <c r="CR3" s="0">
-        <v>0.35422995686531067</v>
+        <v>0.36728602647781372</v>
       </c>
       <c r="CS3" s="0">
-        <v>0.35064980387687683</v>
+        <v>0.29607704281806946</v>
       </c>
       <c r="CT3" s="0">
-        <v>0.32994762063026428</v>
+        <v>0.33016461133956909</v>
       </c>
       <c r="CU3" s="0">
-        <v>0.34117406606674194</v>
+        <v>0.36733913421630859</v>
       </c>
       <c r="CV3" s="0">
-        <v>0.34699630737304688</v>
+        <v>0.33608037233352661</v>
       </c>
       <c r="CW3" s="0">
-        <v>0.34478616714477539</v>
+        <v>0.35580393671989441</v>
       </c>
       <c r="CX3" s="0">
-        <v>0.31577393412590027</v>
+        <v>0.25115522742271423</v>
       </c>
       <c r="CY3" s="0">
-        <v>0.29433172941207886</v>
+        <v>0.2927033007144928</v>
       </c>
       <c r="CZ3" s="0">
-        <v>0.31556424498558044</v>
+        <v>0.3466726541519165</v>
       </c>
       <c r="DA3" s="0">
-        <v>0.32945695519447327</v>
+        <v>0.35231328010559082</v>
       </c>
       <c r="DB3" s="0">
-        <v>0.35277903079986572</v>
+        <v>0.41398429870605469</v>
       </c>
       <c r="DC3" s="0">
-        <v>0.37467053532600403</v>
+        <v>0.24427130818367004</v>
       </c>
       <c r="DD3" s="0">
-        <v>0.29931241273880005</v>
+        <v>0.25003674626350403</v>
       </c>
       <c r="DE3" s="0">
-        <v>0.25957071781158447</v>
+        <v>0.25385922193527222</v>
       </c>
       <c r="DF3" s="0">
-        <v>0.33101540803909302</v>
+        <v>0.34436187148094177</v>
       </c>
       <c r="DG3" s="0">
-        <v>0.33258923888206482</v>
+        <v>0.3856332004070282</v>
       </c>
       <c r="DH3" s="0">
-        <v>0.34537369012832642</v>
+        <v>0.38409709930419922</v>
       </c>
       <c r="DI3" s="0">
-        <v>0.34233775734901428</v>
+        <v>0.35641947388648987</v>
       </c>
       <c r="DJ3" s="0">
-        <v>0.29223966598510742</v>
+        <v>0.24373249709606171</v>
       </c>
       <c r="DK3" s="0">
-        <v>0.32125845551490784</v>
+        <v>0.36364316940307617</v>
       </c>
       <c r="DL3" s="0">
-        <v>0.1816370040178299</v>
+        <v>0.23232236504554749</v>
       </c>
       <c r="DM3" s="0">
-        <v>0.30821108818054199</v>
+        <v>0.34001195430755615</v>
       </c>
       <c r="DN3" s="0">
-        <v>0.37846571207046509</v>
+        <v>0.39043605327606201</v>
       </c>
       <c r="DO3" s="0">
-        <v>0.37517711520195007</v>
+        <v>0.36841797828674317</v>
       </c>
       <c r="DP3" s="0">
-        <v>0.28165042400360107</v>
+        <v>0.26896843314170838</v>
       </c>
       <c r="DQ3" s="0">
-        <v>0.26472181081771851</v>
+        <v>0.30059200525283814</v>
       </c>
       <c r="DR3" s="0">
-        <v>0.30127239227294922</v>
+        <v>0.2857326865196228</v>
       </c>
       <c r="DS3" s="0">
-        <v>0.35080710053443909</v>
+        <v>0.32307970523834229</v>
       </c>
     </row>
     <row r="4">
@@ -1769,364 +1770,364 @@
         <v>25</v>
       </c>
       <c r="D4" s="0">
-        <v>0.22648410499095917</v>
+        <v>0.35519281029701233</v>
       </c>
       <c r="E4" s="0">
-        <v>0.21166010200977325</v>
+        <v>0.32509729266166687</v>
       </c>
       <c r="F4" s="0">
-        <v>0.22548589110374451</v>
+        <v>0.32413610816001892</v>
       </c>
       <c r="G4" s="0">
-        <v>0.18658733367919922</v>
+        <v>0.32064315676689148</v>
       </c>
       <c r="H4" s="0">
-        <v>0.19431188702583313</v>
+        <v>0.3025633692741394</v>
       </c>
       <c r="I4" s="0">
-        <v>0.21597754955291748</v>
+        <v>0.33340960741043091</v>
       </c>
       <c r="J4" s="0">
-        <v>0.18924723565578461</v>
+        <v>0.310355544090271</v>
       </c>
       <c r="K4" s="0">
-        <v>0.21188719570636749</v>
+        <v>0.31930625438690186</v>
       </c>
       <c r="L4" s="0">
-        <v>0.23237010836601257</v>
+        <v>0.33397337794303894</v>
       </c>
       <c r="M4" s="0">
-        <v>0.1943979412317276</v>
+        <v>0.300782710313797</v>
       </c>
       <c r="N4" s="0">
-        <v>0.32051390409469604</v>
+        <v>0.4083952009677887</v>
       </c>
       <c r="O4" s="0">
-        <v>0.25690773129463196</v>
+        <v>0.3664499819278717</v>
       </c>
       <c r="P4" s="0">
-        <v>0.19949695467948914</v>
+        <v>0.28964656591415405</v>
       </c>
       <c r="Q4" s="0">
-        <v>0.21334785223007202</v>
+        <v>0.32626447081565857</v>
       </c>
       <c r="R4" s="0">
-        <v>0.24358361959457397</v>
+        <v>0.36036908626556397</v>
       </c>
       <c r="S4" s="0">
-        <v>0.26026448607444763</v>
+        <v>0.37334194779396057</v>
       </c>
       <c r="T4" s="0">
-        <v>0.1781163364648819</v>
+        <v>0.29548817873001099</v>
       </c>
       <c r="U4" s="0">
-        <v>0.166921466588974</v>
+        <v>0.28317058086395264</v>
       </c>
       <c r="V4" s="0">
-        <v>0.23488564789295197</v>
+        <v>0.3586747944355011</v>
       </c>
       <c r="W4" s="0">
-        <v>0.21392950415611267</v>
+        <v>0.3410625159740448</v>
       </c>
       <c r="X4" s="0">
-        <v>0.38717424869537354</v>
+        <v>0.32425197958946228</v>
       </c>
       <c r="Y4" s="0">
-        <v>0.33838555216789246</v>
+        <v>0.26193833351135254</v>
       </c>
       <c r="Z4" s="0">
-        <v>0.30365923047065735</v>
+        <v>0.33346876502037048</v>
       </c>
       <c r="AA4" s="0">
-        <v>0.34796050190925598</v>
+        <v>0.30722126364707947</v>
       </c>
       <c r="AB4" s="0">
-        <v>0.27421635389328003</v>
+        <v>0.27941864728927612</v>
       </c>
       <c r="AC4" s="0">
-        <v>0.32588210701942444</v>
+        <v>0.27203452587127686</v>
       </c>
       <c r="AD4" s="0">
-        <v>0.26125705242156982</v>
+        <v>0.32861149311065674</v>
       </c>
       <c r="AE4" s="0">
-        <v>0.28535005450248718</v>
+        <v>0.33994859457015991</v>
       </c>
       <c r="AF4" s="0">
-        <v>0.31154569983482361</v>
+        <v>0.2788868248462677</v>
       </c>
       <c r="AG4" s="0">
-        <v>0.30919122695922852</v>
+        <v>0.30852797627449036</v>
       </c>
       <c r="AH4" s="0">
-        <v>0.41157686710357666</v>
+        <v>0.38551211357116699</v>
       </c>
       <c r="AI4" s="0">
-        <v>0.33977252244949341</v>
+        <v>0.26202443242073059</v>
       </c>
       <c r="AJ4" s="0">
-        <v>0.35243451595306396</v>
+        <v>0.36479124426841736</v>
       </c>
       <c r="AK4" s="0">
-        <v>0.27690291404724121</v>
+        <v>0.2916300892829895</v>
       </c>
       <c r="AL4" s="0">
-        <v>0.32829701900482178</v>
+        <v>0.3246232271194458</v>
       </c>
       <c r="AM4" s="0">
-        <v>0.33499747514724731</v>
+        <v>0.28861427307128906</v>
       </c>
       <c r="AN4" s="0">
-        <v>0.33515432476997375</v>
+        <v>0.34249553084373474</v>
       </c>
       <c r="AO4" s="0">
-        <v>0.34890204668045044</v>
+        <v>0.35424593091011047</v>
       </c>
       <c r="AP4" s="0">
-        <v>0.32665297389030457</v>
+        <v>0.29391577839851379</v>
       </c>
       <c r="AQ4" s="0">
-        <v>0.32655787467956543</v>
+        <v>0.29267570376396179</v>
       </c>
       <c r="AR4" s="0">
-        <v>0.31053483486175537</v>
+        <v>0.31697583198547363</v>
       </c>
       <c r="AS4" s="0">
-        <v>0.28959420323371887</v>
+        <v>0.29792392253875732</v>
       </c>
       <c r="AT4" s="0">
-        <v>0.352314293384552</v>
+        <v>0.27720654010772705</v>
       </c>
       <c r="AU4" s="0">
-        <v>0.33508053421974182</v>
+        <v>0.37632346153259277</v>
       </c>
       <c r="AV4" s="0">
-        <v>0.33787447214126587</v>
+        <v>0.28501540422439575</v>
       </c>
       <c r="AW4" s="0">
-        <v>0.30759567022323608</v>
+        <v>0.2841109037399292</v>
       </c>
       <c r="AX4" s="0">
-        <v>0.37151789665222168</v>
+        <v>0.3072834312915802</v>
       </c>
       <c r="AY4" s="0">
-        <v>0.34742546081542969</v>
+        <v>0.34985876083374023</v>
       </c>
       <c r="AZ4" s="0">
-        <v>0.32928743958473206</v>
+        <v>0.30987370014190674</v>
       </c>
       <c r="BA4" s="0">
-        <v>0.33825698494911194</v>
+        <v>0.25865566730499268</v>
       </c>
       <c r="BB4" s="0">
-        <v>0.29644298553466797</v>
+        <v>0.28194254636764526</v>
       </c>
       <c r="BC4" s="0">
-        <v>0.3373928964138031</v>
+        <v>0.34856557846069336</v>
       </c>
       <c r="BD4" s="0">
-        <v>0.34298074245452881</v>
+        <v>0.30190542340278625</v>
       </c>
       <c r="BE4" s="0">
-        <v>0.31839880347251892</v>
+        <v>0.310008704662323</v>
       </c>
       <c r="BF4" s="0">
-        <v>0.40555933117866516</v>
+        <v>0.32106024026870728</v>
       </c>
       <c r="BG4" s="0">
-        <v>0.41880694031715393</v>
+        <v>0.29870226979255676</v>
       </c>
       <c r="BH4" s="0">
-        <v>0.40473726391792297</v>
+        <v>0.26854115724563599</v>
       </c>
       <c r="BI4" s="0">
-        <v>0.39742520451545715</v>
+        <v>0.28601378202438355</v>
       </c>
       <c r="BJ4" s="0">
-        <v>0.28431230783462524</v>
+        <v>0.31149348616600037</v>
       </c>
       <c r="BK4" s="0">
-        <v>0.36552777886390686</v>
+        <v>0.26929968595504761</v>
       </c>
       <c r="BL4" s="0">
-        <v>0.35435083508491516</v>
+        <v>0.38079994916915894</v>
       </c>
       <c r="BM4" s="0">
-        <v>0.41516315937042236</v>
+        <v>0.33511301875114441</v>
       </c>
       <c r="BN4" s="0">
-        <v>0.37361308932304382</v>
+        <v>0.29023116827011108</v>
       </c>
       <c r="BO4" s="0">
-        <v>0.33362329006195068</v>
+        <v>0.39535537362098694</v>
       </c>
       <c r="BP4" s="0">
-        <v>0.32456779479980469</v>
+        <v>0.33960315585136414</v>
       </c>
       <c r="BQ4" s="0">
-        <v>0.39715132117271423</v>
+        <v>0.29929062724113464</v>
       </c>
       <c r="BR4" s="0">
-        <v>0.33267214894294739</v>
+        <v>0.27152827382087708</v>
       </c>
       <c r="BS4" s="0">
-        <v>0.38153278827667236</v>
+        <v>0.35463422536849976</v>
       </c>
       <c r="BT4" s="0">
-        <v>0.31995293498039246</v>
+        <v>0.31719473004341126</v>
       </c>
       <c r="BU4" s="0">
-        <v>0.31446853280067444</v>
+        <v>0.39223992824554443</v>
       </c>
       <c r="BV4" s="0">
-        <v>0.40460050106048584</v>
+        <v>0.31239581108093262</v>
       </c>
       <c r="BW4" s="0">
-        <v>0.38120242953300476</v>
+        <v>0.36787477135658264</v>
       </c>
       <c r="BX4" s="0">
-        <v>0.36253109574317932</v>
+        <v>0.32912448048591614</v>
       </c>
       <c r="BY4" s="0">
-        <v>0.34245726466178894</v>
+        <v>0.32087260484695435</v>
       </c>
       <c r="BZ4" s="0">
-        <v>0.36046516895294189</v>
+        <v>0.36126112937927246</v>
       </c>
       <c r="CA4" s="0">
-        <v>0.38765978813171387</v>
+        <v>0.36045685410499573</v>
       </c>
       <c r="CB4" s="0">
-        <v>0.40977028012275696</v>
+        <v>0.35479950904846191</v>
       </c>
       <c r="CC4" s="0">
-        <v>0.38394758105278015</v>
+        <v>0.3492293655872345</v>
       </c>
       <c r="CD4" s="0">
-        <v>0.27711212635040283</v>
+        <v>0.24585142731666565</v>
       </c>
       <c r="CE4" s="0">
-        <v>0.32094618678092957</v>
+        <v>0.3810361921787262</v>
       </c>
       <c r="CF4" s="0">
-        <v>0.36023980379104614</v>
+        <v>0.33769434690475464</v>
       </c>
       <c r="CG4" s="0">
-        <v>0.42303532361984253</v>
+        <v>0.31760627031326294</v>
       </c>
       <c r="CH4" s="0">
-        <v>0.2718869149684906</v>
+        <v>0.27851530909538269</v>
       </c>
       <c r="CI4" s="0">
-        <v>0.30919724702835083</v>
+        <v>0.30063694715499878</v>
       </c>
       <c r="CJ4" s="0">
-        <v>0.32969245314598083</v>
+        <v>0.3270900547504425</v>
       </c>
       <c r="CK4" s="0">
-        <v>0.38685622811317444</v>
+        <v>0.31872215867042542</v>
       </c>
       <c r="CL4" s="0">
-        <v>0.36263519525527954</v>
+        <v>0.29702603816986084</v>
       </c>
       <c r="CM4" s="0">
-        <v>0.37036606669425964</v>
+        <v>0.29188954830169678</v>
       </c>
       <c r="CN4" s="0">
-        <v>0.42828109860420227</v>
+        <v>0.37836536765098572</v>
       </c>
       <c r="CO4" s="0">
-        <v>0.35378921031951904</v>
+        <v>0.31293714046478272</v>
       </c>
       <c r="CP4" s="0">
-        <v>0.38768658041954041</v>
+        <v>0.33183020353317261</v>
       </c>
       <c r="CQ4" s="0">
-        <v>0.33808308839797974</v>
+        <v>0.27537152171134949</v>
       </c>
       <c r="CR4" s="0">
-        <v>0.32329225540161133</v>
+        <v>0.35590514540672302</v>
       </c>
       <c r="CS4" s="0">
-        <v>0.29916420578956604</v>
+        <v>0.30853033065795898</v>
       </c>
       <c r="CT4" s="0">
-        <v>0.30900004506111145</v>
+        <v>0.3557828962802887</v>
       </c>
       <c r="CU4" s="0">
-        <v>0.33707109093666077</v>
+        <v>0.34749191999435425</v>
       </c>
       <c r="CV4" s="0">
-        <v>0.34753456711769104</v>
+        <v>0.33606436848640442</v>
       </c>
       <c r="CW4" s="0">
-        <v>0.31743010878562927</v>
+        <v>0.30956128239631653</v>
       </c>
       <c r="CX4" s="0">
-        <v>0.29473859071731567</v>
+        <v>0.25783157348632813</v>
       </c>
       <c r="CY4" s="0">
-        <v>0.32074061036109924</v>
+        <v>0.2973247766494751</v>
       </c>
       <c r="CZ4" s="0">
-        <v>0.35371223092079163</v>
+        <v>0.34215474128723145</v>
       </c>
       <c r="DA4" s="0">
-        <v>0.35384136438369751</v>
+        <v>0.28618738055229187</v>
       </c>
       <c r="DB4" s="0">
-        <v>0.31182682514190674</v>
+        <v>0.35934916138648987</v>
       </c>
       <c r="DC4" s="0">
-        <v>0.38742759823799133</v>
+        <v>0.29828909039497376</v>
       </c>
       <c r="DD4" s="0">
-        <v>0.31184229254722595</v>
+        <v>0.26759126782417297</v>
       </c>
       <c r="DE4" s="0">
-        <v>0.23746679723262787</v>
+        <v>0.25048059225082397</v>
       </c>
       <c r="DF4" s="0">
-        <v>0.38422027230262756</v>
+        <v>0.32992801070213318</v>
       </c>
       <c r="DG4" s="0">
-        <v>0.4209463894367218</v>
+        <v>0.35410374402999878</v>
       </c>
       <c r="DH4" s="0">
-        <v>0.40578889846801758</v>
+        <v>0.38118270039558411</v>
       </c>
       <c r="DI4" s="0">
-        <v>0.37740308046340942</v>
+        <v>0.37412652373313904</v>
       </c>
       <c r="DJ4" s="0">
-        <v>0.3324374258518219</v>
+        <v>0.28651818633079529</v>
       </c>
       <c r="DK4" s="0">
-        <v>0.3913760781288147</v>
+        <v>0.31808385252952576</v>
       </c>
       <c r="DL4" s="0">
-        <v>0.20554584264755249</v>
+        <v>0.26071706414222717</v>
       </c>
       <c r="DM4" s="0">
-        <v>0.41037571430206299</v>
+        <v>0.29516911506652832</v>
       </c>
       <c r="DN4" s="0">
-        <v>0.40095669031143188</v>
+        <v>0.36659747362136841</v>
       </c>
       <c r="DO4" s="0">
-        <v>0.3895021378993988</v>
+        <v>0.3822188675403595</v>
       </c>
       <c r="DP4" s="0">
-        <v>0.31887629628181458</v>
+        <v>0.34263026714324951</v>
       </c>
       <c r="DQ4" s="0">
-        <v>0.30566459894180298</v>
+        <v>0.30441936850547791</v>
       </c>
       <c r="DR4" s="0">
-        <v>0.33721309900283813</v>
+        <v>0.27693164348602295</v>
       </c>
       <c r="DS4" s="0">
-        <v>0.33133316040039062</v>
+        <v>0.32645565271377563</v>
       </c>
     </row>
     <row r="5">
@@ -2140,364 +2141,364 @@
         <v>26</v>
       </c>
       <c r="D5" s="0">
-        <v>0.29468229413032532</v>
+        <v>0.41660767793655396</v>
       </c>
       <c r="E5" s="0">
-        <v>0.28345361351966858</v>
+        <v>0.41448450088500977</v>
       </c>
       <c r="F5" s="0">
-        <v>0.29453861713409424</v>
+        <v>0.40257793664932251</v>
       </c>
       <c r="G5" s="0">
-        <v>0.28357094526290894</v>
+        <v>0.39127719402313233</v>
       </c>
       <c r="H5" s="0">
-        <v>0.27602431178092957</v>
+        <v>0.38768690824508667</v>
       </c>
       <c r="I5" s="0">
-        <v>0.28748664259910583</v>
+        <v>0.38883599638938904</v>
       </c>
       <c r="J5" s="0">
-        <v>0.26951935887336731</v>
+        <v>0.38021489977836609</v>
       </c>
       <c r="K5" s="0">
-        <v>0.27131643891334534</v>
+        <v>0.38981842994689941</v>
       </c>
       <c r="L5" s="0">
-        <v>0.29856070876121521</v>
+        <v>0.40917837619781494</v>
       </c>
       <c r="M5" s="0">
-        <v>0.275217205286026</v>
+        <v>0.40035605430603027</v>
       </c>
       <c r="N5" s="0">
-        <v>0.34594380855560303</v>
+        <v>0.48372381925582886</v>
       </c>
       <c r="O5" s="0">
-        <v>0.33245643973350525</v>
+        <v>0.44510450959205627</v>
       </c>
       <c r="P5" s="0">
-        <v>0.25241824984550476</v>
+        <v>0.37425673007965088</v>
       </c>
       <c r="Q5" s="0">
-        <v>0.28177288174629211</v>
+        <v>0.42335957288742066</v>
       </c>
       <c r="R5" s="0">
-        <v>0.33424913883209229</v>
+        <v>0.45807868242263794</v>
       </c>
       <c r="S5" s="0">
-        <v>0.33278438448905945</v>
+        <v>0.45429793000221253</v>
       </c>
       <c r="T5" s="0">
-        <v>0.23481430113315582</v>
+        <v>0.36872884631156921</v>
       </c>
       <c r="U5" s="0">
-        <v>0.21863587200641632</v>
+        <v>0.36380979418754578</v>
       </c>
       <c r="V5" s="0">
-        <v>0.3272135853767395</v>
+        <v>0.43664932250976563</v>
       </c>
       <c r="W5" s="0">
-        <v>0.29419109225273132</v>
+        <v>0.38336005806922913</v>
       </c>
       <c r="X5" s="0">
-        <v>0.35862591862678528</v>
+        <v>0.32124057412147522</v>
       </c>
       <c r="Y5" s="0">
-        <v>0.34549835324287415</v>
+        <v>0.34581494331359863</v>
       </c>
       <c r="Z5" s="0">
-        <v>0.39444029331207275</v>
+        <v>0.34067991375923157</v>
       </c>
       <c r="AA5" s="0">
-        <v>0.36109092831611633</v>
+        <v>0.32328048348426819</v>
       </c>
       <c r="AB5" s="0">
-        <v>0.36797776818275452</v>
+        <v>0.32313272356987</v>
       </c>
       <c r="AC5" s="0">
-        <v>0.36279967427253723</v>
+        <v>0.33928990364074707</v>
       </c>
       <c r="AD5" s="0">
-        <v>0.34968027472496033</v>
+        <v>0.30156800150871277</v>
       </c>
       <c r="AE5" s="0">
-        <v>0.28298604488372803</v>
+        <v>0.30848297476768494</v>
       </c>
       <c r="AF5" s="0">
-        <v>0.27323561906814575</v>
+        <v>0.21038563549518585</v>
       </c>
       <c r="AG5" s="0">
-        <v>0.28268745541572571</v>
+        <v>0.25026324391365051</v>
       </c>
       <c r="AH5" s="0">
-        <v>0.37230220437049866</v>
+        <v>0.3834499716758728</v>
       </c>
       <c r="AI5" s="0">
-        <v>0.31846827268600464</v>
+        <v>0.27926501631736755</v>
       </c>
       <c r="AJ5" s="0">
-        <v>0.34301486611366272</v>
+        <v>0.31635084748268128</v>
       </c>
       <c r="AK5" s="0">
-        <v>0.35188305377960205</v>
+        <v>0.21991842985153198</v>
       </c>
       <c r="AL5" s="0">
-        <v>0.34254392981529236</v>
+        <v>0.3520052433013916</v>
       </c>
       <c r="AM5" s="0">
-        <v>0.38481622934341431</v>
+        <v>0.34559744596481323</v>
       </c>
       <c r="AN5" s="0">
-        <v>0.34644383192062378</v>
+        <v>0.37262332439422607</v>
       </c>
       <c r="AO5" s="0">
-        <v>0.28973647952079773</v>
+        <v>0.40125072002410889</v>
       </c>
       <c r="AP5" s="0">
-        <v>0.29981282353401184</v>
+        <v>0.31329354643821716</v>
       </c>
       <c r="AQ5" s="0">
-        <v>0.34141355752944946</v>
+        <v>0.24419727921485901</v>
       </c>
       <c r="AR5" s="0">
-        <v>0.29198673367500305</v>
+        <v>0.2371499240398407</v>
       </c>
       <c r="AS5" s="0">
-        <v>0.36727160215377808</v>
+        <v>0.23282505571842194</v>
       </c>
       <c r="AT5" s="0">
-        <v>0.30743959546089172</v>
+        <v>0.30901721119880676</v>
       </c>
       <c r="AU5" s="0">
-        <v>0.34560227394104004</v>
+        <v>0.31100732088088989</v>
       </c>
       <c r="AV5" s="0">
-        <v>0.37913051247596741</v>
+        <v>0.28717726469039917</v>
       </c>
       <c r="AW5" s="0">
-        <v>0.35889872908592224</v>
+        <v>0.32332265377044678</v>
       </c>
       <c r="AX5" s="0">
-        <v>0.40590715408325195</v>
+        <v>0.33584383130073547</v>
       </c>
       <c r="AY5" s="0">
-        <v>0.36334326863288879</v>
+        <v>0.33725693821907044</v>
       </c>
       <c r="AZ5" s="0">
-        <v>0.36887973546981812</v>
+        <v>0.30712705850601196</v>
       </c>
       <c r="BA5" s="0">
-        <v>0.31125786900520325</v>
+        <v>0.31489807367324829</v>
       </c>
       <c r="BB5" s="0">
-        <v>0.35124808549880981</v>
+        <v>0.34701639413833618</v>
       </c>
       <c r="BC5" s="0">
-        <v>0.31633365154266357</v>
+        <v>0.41172105073928833</v>
       </c>
       <c r="BD5" s="0">
-        <v>0.316130131483078</v>
+        <v>0.31653043627738953</v>
       </c>
       <c r="BE5" s="0">
-        <v>0.29250466823577881</v>
+        <v>0.34185042977333069</v>
       </c>
       <c r="BF5" s="0">
-        <v>0.341146320104599</v>
+        <v>0.30355527997016907</v>
       </c>
       <c r="BG5" s="0">
-        <v>0.37319734692573547</v>
+        <v>0.3323327898979187</v>
       </c>
       <c r="BH5" s="0">
-        <v>0.3609614372253418</v>
+        <v>0.32911154627799988</v>
       </c>
       <c r="BI5" s="0">
-        <v>0.316245436668396</v>
+        <v>0.3069281280040741</v>
       </c>
       <c r="BJ5" s="0">
-        <v>0.30363771319389343</v>
+        <v>0.26078113913536072</v>
       </c>
       <c r="BK5" s="0">
-        <v>0.29875209927558899</v>
+        <v>0.3425716757774353</v>
       </c>
       <c r="BL5" s="0">
-        <v>0.2974240779876709</v>
+        <v>0.33351346850395203</v>
       </c>
       <c r="BM5" s="0">
-        <v>0.35051420331001282</v>
+        <v>0.36577221751213074</v>
       </c>
       <c r="BN5" s="0">
-        <v>0.37646934390068054</v>
+        <v>0.3080691397190094</v>
       </c>
       <c r="BO5" s="0">
-        <v>0.32466867566108704</v>
+        <v>0.35888364911079407</v>
       </c>
       <c r="BP5" s="0">
-        <v>0.39021307229995728</v>
+        <v>0.3209080696105957</v>
       </c>
       <c r="BQ5" s="0">
-        <v>0.38221144676208496</v>
+        <v>0.30461189150810242</v>
       </c>
       <c r="BR5" s="0">
-        <v>0.31409910321235657</v>
+        <v>0.34911924600601196</v>
       </c>
       <c r="BS5" s="0">
-        <v>0.36150312423706055</v>
+        <v>0.29485869407653809</v>
       </c>
       <c r="BT5" s="0">
-        <v>0.32988479733467102</v>
+        <v>0.29024899005889893</v>
       </c>
       <c r="BU5" s="0">
-        <v>0.33678114414215088</v>
+        <v>0.33660146594047546</v>
       </c>
       <c r="BV5" s="0">
-        <v>0.38188156485557556</v>
+        <v>0.34995725750923157</v>
       </c>
       <c r="BW5" s="0">
-        <v>0.30237051844596863</v>
+        <v>0.34846487641334534</v>
       </c>
       <c r="BX5" s="0">
-        <v>0.36748731136322021</v>
+        <v>0.37331044673919678</v>
       </c>
       <c r="BY5" s="0">
-        <v>0.38273698091506958</v>
+        <v>0.35544416308403015</v>
       </c>
       <c r="BZ5" s="0">
-        <v>0.40119415521621704</v>
+        <v>0.33984661102294922</v>
       </c>
       <c r="CA5" s="0">
-        <v>0.36430048942565918</v>
+        <v>0.37806007266044617</v>
       </c>
       <c r="CB5" s="0">
-        <v>0.35671135783195496</v>
+        <v>0.35490122437477112</v>
       </c>
       <c r="CC5" s="0">
-        <v>0.36594641208648682</v>
+        <v>0.31814113259315491</v>
       </c>
       <c r="CD5" s="0">
-        <v>0.28192421793937683</v>
+        <v>0.26849484443664551</v>
       </c>
       <c r="CE5" s="0">
-        <v>0.34041288495063782</v>
+        <v>0.30736282467842102</v>
       </c>
       <c r="CF5" s="0">
-        <v>0.35408923029899597</v>
+        <v>0.35632151365280151</v>
       </c>
       <c r="CG5" s="0">
-        <v>0.3190956711769104</v>
+        <v>0.28631570935249329</v>
       </c>
       <c r="CH5" s="0">
-        <v>0.26872560381889343</v>
+        <v>0.20961518585681915</v>
       </c>
       <c r="CI5" s="0">
-        <v>0.29808986186981201</v>
+        <v>0.28561070561408997</v>
       </c>
       <c r="CJ5" s="0">
-        <v>0.33395683765411377</v>
+        <v>0.3037172257900238</v>
       </c>
       <c r="CK5" s="0">
-        <v>0.33302527666091919</v>
+        <v>0.36429855227470398</v>
       </c>
       <c r="CL5" s="0">
-        <v>0.33290496468544006</v>
+        <v>0.34810313582420349</v>
       </c>
       <c r="CM5" s="0">
-        <v>0.30899754166603088</v>
+        <v>0.33625560998916626</v>
       </c>
       <c r="CN5" s="0">
-        <v>0.28938037157058716</v>
+        <v>0.28317108750343323</v>
       </c>
       <c r="CO5" s="0">
-        <v>0.33094701170921326</v>
+        <v>0.3435322642326355</v>
       </c>
       <c r="CP5" s="0">
-        <v>0.34534618258476257</v>
+        <v>0.39177200198173523</v>
       </c>
       <c r="CQ5" s="0">
-        <v>0.29661998152732849</v>
+        <v>0.28171899914741516</v>
       </c>
       <c r="CR5" s="0">
-        <v>0.33784466981887817</v>
+        <v>0.34186378121376038</v>
       </c>
       <c r="CS5" s="0">
-        <v>0.3159959614276886</v>
+        <v>0.33286890387535095</v>
       </c>
       <c r="CT5" s="0">
-        <v>0.34758093953132629</v>
+        <v>0.28039208054542542</v>
       </c>
       <c r="CU5" s="0">
-        <v>0.35884591937065125</v>
+        <v>0.30242684483528137</v>
       </c>
       <c r="CV5" s="0">
-        <v>0.38128009438514709</v>
+        <v>0.28126215934753418</v>
       </c>
       <c r="CW5" s="0">
-        <v>0.41074490547180176</v>
+        <v>0.31600925326347351</v>
       </c>
       <c r="CX5" s="0">
-        <v>0.29429766535758972</v>
+        <v>0.27629572153091431</v>
       </c>
       <c r="CY5" s="0">
-        <v>0.2381858229637146</v>
+        <v>0.2739664614200592</v>
       </c>
       <c r="CZ5" s="0">
-        <v>0.33895236253738403</v>
+        <v>0.33280187845230103</v>
       </c>
       <c r="DA5" s="0">
-        <v>0.33563154935836792</v>
+        <v>0.30109328031539917</v>
       </c>
       <c r="DB5" s="0">
-        <v>0.34587952494621277</v>
+        <v>0.29253479838371277</v>
       </c>
       <c r="DC5" s="0">
-        <v>0.35089516639709473</v>
+        <v>0.26663702726364136</v>
       </c>
       <c r="DD5" s="0">
-        <v>0.28046911954879761</v>
+        <v>0.26795440912246704</v>
       </c>
       <c r="DE5" s="0">
-        <v>0.26019886136054993</v>
+        <v>0.21902225911617279</v>
       </c>
       <c r="DF5" s="0">
-        <v>0.36466756463050842</v>
+        <v>0.32528293132781983</v>
       </c>
       <c r="DG5" s="0">
-        <v>0.35787051916122437</v>
+        <v>0.34956660866737366</v>
       </c>
       <c r="DH5" s="0">
-        <v>0.39041018486022949</v>
+        <v>0.3563692569732666</v>
       </c>
       <c r="DI5" s="0">
-        <v>0.34228074550628662</v>
+        <v>0.30176648497581482</v>
       </c>
       <c r="DJ5" s="0">
-        <v>0.33260780572891235</v>
+        <v>0.28432255983352661</v>
       </c>
       <c r="DK5" s="0">
-        <v>0.34916675090789795</v>
+        <v>0.37052777409553528</v>
       </c>
       <c r="DL5" s="0">
-        <v>0.20636370778083801</v>
+        <v>0.16055074334144592</v>
       </c>
       <c r="DM5" s="0">
-        <v>0.39852520823478699</v>
+        <v>0.37121498584747315</v>
       </c>
       <c r="DN5" s="0">
-        <v>0.39428570866584778</v>
+        <v>0.40015774965286255</v>
       </c>
       <c r="DO5" s="0">
-        <v>0.39705643057823181</v>
+        <v>0.35883337259292603</v>
       </c>
       <c r="DP5" s="0">
-        <v>0.25212118029594421</v>
+        <v>0.2990909218788147</v>
       </c>
       <c r="DQ5" s="0">
-        <v>0.30977019667625427</v>
+        <v>0.27599585056304932</v>
       </c>
       <c r="DR5" s="0">
-        <v>0.26956468820571899</v>
+        <v>0.2491302490234375</v>
       </c>
       <c r="DS5" s="0">
-        <v>0.28769943118095398</v>
+        <v>0.24633455276489258</v>
       </c>
     </row>
     <row r="6">
@@ -2511,364 +2512,364 @@
         <v>27</v>
       </c>
       <c r="D6" s="0">
-        <v>0.31250393390655518</v>
+        <v>0.37367171049118042</v>
       </c>
       <c r="E6" s="0">
-        <v>0.3079962432384491</v>
+        <v>0.35992822051048279</v>
       </c>
       <c r="F6" s="0">
-        <v>0.30831870436668396</v>
+        <v>0.34333270788192749</v>
       </c>
       <c r="G6" s="0">
-        <v>0.27977612614631653</v>
+        <v>0.31029602885246277</v>
       </c>
       <c r="H6" s="0">
-        <v>0.28824397921562195</v>
+        <v>0.34461438655853272</v>
       </c>
       <c r="I6" s="0">
-        <v>0.29166948795318604</v>
+        <v>0.35929647088050842</v>
       </c>
       <c r="J6" s="0">
-        <v>0.27663633227348328</v>
+        <v>0.34378647804260254</v>
       </c>
       <c r="K6" s="0">
-        <v>0.27314507961273193</v>
+        <v>0.32618606090545654</v>
       </c>
       <c r="L6" s="0">
-        <v>0.31540554761886597</v>
+        <v>0.35916951298713684</v>
       </c>
       <c r="M6" s="0">
-        <v>0.27677470445632935</v>
+        <v>0.33007168769836426</v>
       </c>
       <c r="N6" s="0">
-        <v>0.37523794174194336</v>
+        <v>0.42604038119316101</v>
       </c>
       <c r="O6" s="0">
-        <v>0.33293354511260986</v>
+        <v>0.40810242295265198</v>
       </c>
       <c r="P6" s="0">
-        <v>0.27009931206703186</v>
+        <v>0.33365005254745483</v>
       </c>
       <c r="Q6" s="0">
-        <v>0.29287990927696228</v>
+        <v>0.36778667569160461</v>
       </c>
       <c r="R6" s="0">
-        <v>0.33376038074493408</v>
+        <v>0.37141025066375732</v>
       </c>
       <c r="S6" s="0">
-        <v>0.34288215637207031</v>
+        <v>0.39623314142227173</v>
       </c>
       <c r="T6" s="0">
-        <v>0.25774314999580383</v>
+        <v>0.30978047847747803</v>
       </c>
       <c r="U6" s="0">
-        <v>0.25335538387298584</v>
+        <v>0.32286325097084045</v>
       </c>
       <c r="V6" s="0">
-        <v>0.33562082052230835</v>
+        <v>0.37810805439949036</v>
       </c>
       <c r="W6" s="0">
-        <v>0.29188144207000732</v>
+        <v>0.35715815424919129</v>
       </c>
       <c r="X6" s="0">
-        <v>0.30951386690139771</v>
+        <v>0.36416319012641907</v>
       </c>
       <c r="Y6" s="0">
-        <v>0.30028486251831055</v>
+        <v>0.37535324692726135</v>
       </c>
       <c r="Z6" s="0">
-        <v>0.37513208389282227</v>
+        <v>0.3792814314365387</v>
       </c>
       <c r="AA6" s="0">
-        <v>0.37262195348739624</v>
+        <v>0.33327183127403259</v>
       </c>
       <c r="AB6" s="0">
-        <v>0.28583899140357971</v>
+        <v>0.3097347617149353</v>
       </c>
       <c r="AC6" s="0">
-        <v>0.32178795337677002</v>
+        <v>0.33862677216529846</v>
       </c>
       <c r="AD6" s="0">
-        <v>0.33410999178886414</v>
+        <v>0.32051774859428406</v>
       </c>
       <c r="AE6" s="0">
-        <v>0.36586037278175354</v>
+        <v>0.37596136331558228</v>
       </c>
       <c r="AF6" s="0">
-        <v>0.35218319296836853</v>
+        <v>0.31272125244140625</v>
       </c>
       <c r="AG6" s="0">
-        <v>0.3420960009098053</v>
+        <v>0.29066336154937744</v>
       </c>
       <c r="AH6" s="0">
-        <v>0.41810527443885803</v>
+        <v>0.34412884712219238</v>
       </c>
       <c r="AI6" s="0">
-        <v>0.31704860925674438</v>
+        <v>0.31286665797233582</v>
       </c>
       <c r="AJ6" s="0">
-        <v>0.33219197392463684</v>
+        <v>0.37375050783157349</v>
       </c>
       <c r="AK6" s="0">
-        <v>0.33466041088104248</v>
+        <v>0.3246002197265625</v>
       </c>
       <c r="AL6" s="0">
-        <v>0.36991026997566223</v>
+        <v>0.3703649640083313</v>
       </c>
       <c r="AM6" s="0">
-        <v>0.36108621954917908</v>
+        <v>0.32311543822288513</v>
       </c>
       <c r="AN6" s="0">
-        <v>0.35767242312431335</v>
+        <v>0.36338013410568237</v>
       </c>
       <c r="AO6" s="0">
-        <v>0.37937217950820923</v>
+        <v>0.35700953006744385</v>
       </c>
       <c r="AP6" s="0">
-        <v>0.36720827221870422</v>
+        <v>0.30427750945091248</v>
       </c>
       <c r="AQ6" s="0">
-        <v>0.33048141002655029</v>
+        <v>0.30494818091392517</v>
       </c>
       <c r="AR6" s="0">
-        <v>0.34234499931335449</v>
+        <v>0.31542524695396423</v>
       </c>
       <c r="AS6" s="0">
-        <v>0.32858222723007202</v>
+        <v>0.24384649097919464</v>
       </c>
       <c r="AT6" s="0">
-        <v>0.36541905999183655</v>
+        <v>0.35363781452178955</v>
       </c>
       <c r="AU6" s="0">
-        <v>0.39784261584281921</v>
+        <v>0.36036786437034607</v>
       </c>
       <c r="AV6" s="0">
-        <v>0.36273100972175598</v>
+        <v>0.30011174082756043</v>
       </c>
       <c r="AW6" s="0">
-        <v>0.33902636170387268</v>
+        <v>0.34914097189903259</v>
       </c>
       <c r="AX6" s="0">
-        <v>0.37622126936912537</v>
+        <v>0.32498070597648621</v>
       </c>
       <c r="AY6" s="0">
-        <v>0.41055148839950562</v>
+        <v>0.38875219225883484</v>
       </c>
       <c r="AZ6" s="0">
-        <v>0.35337868332862854</v>
+        <v>0.3380374014377594</v>
       </c>
       <c r="BA6" s="0">
-        <v>0.32438379526138306</v>
+        <v>0.29308456182479858</v>
       </c>
       <c r="BB6" s="0">
-        <v>0.35790932178497314</v>
+        <v>0.38718259334564209</v>
       </c>
       <c r="BC6" s="0">
-        <v>0.31238701939582825</v>
+        <v>0.38071447610855103</v>
       </c>
       <c r="BD6" s="0">
-        <v>0.30875897407531738</v>
+        <v>0.35264307260513306</v>
       </c>
       <c r="BE6" s="0">
-        <v>0.32866469025611877</v>
+        <v>0.41294386982917786</v>
       </c>
       <c r="BF6" s="0">
-        <v>0.45382839441299438</v>
+        <v>0.37117940187454224</v>
       </c>
       <c r="BG6" s="0">
-        <v>0.34724551439285278</v>
+        <v>0.38627609610557556</v>
       </c>
       <c r="BH6" s="0">
-        <v>0.33161059021949768</v>
+        <v>0.36034289002418518</v>
       </c>
       <c r="BI6" s="0">
-        <v>0.35899350047111511</v>
+        <v>0.35907348990440369</v>
       </c>
       <c r="BJ6" s="0">
-        <v>0.41040512919425964</v>
+        <v>0.30723011493682861</v>
       </c>
       <c r="BK6" s="0">
-        <v>0.33077123761177063</v>
+        <v>0.36988970637321472</v>
       </c>
       <c r="BL6" s="0">
-        <v>0.31980633735656738</v>
+        <v>0.33264109492301941</v>
       </c>
       <c r="BM6" s="0">
-        <v>0.35084590315818787</v>
+        <v>0.34170955419540405</v>
       </c>
       <c r="BN6" s="0">
-        <v>0.39450892806053162</v>
+        <v>0.41991612315177918</v>
       </c>
       <c r="BO6" s="0">
-        <v>0.38272640109062195</v>
+        <v>0.33621731400489807</v>
       </c>
       <c r="BP6" s="0">
-        <v>0.32062673568725586</v>
+        <v>0.34595930576324463</v>
       </c>
       <c r="BQ6" s="0">
-        <v>0.39094099402427673</v>
+        <v>0.38788062334060669</v>
       </c>
       <c r="BR6" s="0">
-        <v>0.36577460169792175</v>
+        <v>0.37156856060028076</v>
       </c>
       <c r="BS6" s="0">
-        <v>0.33266177773475647</v>
+        <v>0.35879004001617432</v>
       </c>
       <c r="BT6" s="0">
-        <v>0.3858599066734314</v>
+        <v>0.38364973664283752</v>
       </c>
       <c r="BU6" s="0">
-        <v>0.36867484450340271</v>
+        <v>0.35057452321052551</v>
       </c>
       <c r="BV6" s="0">
-        <v>0.35331743955612183</v>
+        <v>0.39928513765335083</v>
       </c>
       <c r="BW6" s="0">
-        <v>0.3287585973739624</v>
+        <v>0.35045352578163147</v>
       </c>
       <c r="BX6" s="0">
-        <v>0.41466218233108521</v>
+        <v>0.34844163060188294</v>
       </c>
       <c r="BY6" s="0">
-        <v>0.38371014595031738</v>
+        <v>0.40049400925636292</v>
       </c>
       <c r="BZ6" s="0">
-        <v>0.4230000376701355</v>
+        <v>0.3501012921333313</v>
       </c>
       <c r="CA6" s="0">
-        <v>0.38148224353790283</v>
+        <v>0.38238668441772461</v>
       </c>
       <c r="CB6" s="0">
-        <v>0.34594330191612244</v>
+        <v>0.35388785600662232</v>
       </c>
       <c r="CC6" s="0">
-        <v>0.34775403141975403</v>
+        <v>0.31809130311012268</v>
       </c>
       <c r="CD6" s="0">
-        <v>0.34009578824043274</v>
+        <v>0.38598060607910156</v>
       </c>
       <c r="CE6" s="0">
-        <v>0.32264772057533264</v>
+        <v>0.32621210813522339</v>
       </c>
       <c r="CF6" s="0">
-        <v>0.41321533918380737</v>
+        <v>0.32702222466468811</v>
       </c>
       <c r="CG6" s="0">
-        <v>0.36081013083457947</v>
+        <v>0.40982303023338318</v>
       </c>
       <c r="CH6" s="0">
-        <v>0.24425645172595978</v>
+        <v>0.32810834050178528</v>
       </c>
       <c r="CI6" s="0">
-        <v>0.23202899098396301</v>
+        <v>0.27827072143554688</v>
       </c>
       <c r="CJ6" s="0">
-        <v>0.25212550163269043</v>
+        <v>0.37022119760513306</v>
       </c>
       <c r="CK6" s="0">
-        <v>0.39451518654823303</v>
+        <v>0.34059590101242066</v>
       </c>
       <c r="CL6" s="0">
-        <v>0.37261888384819031</v>
+        <v>0.357704758644104</v>
       </c>
       <c r="CM6" s="0">
-        <v>0.35059705376625061</v>
+        <v>0.37360912561416626</v>
       </c>
       <c r="CN6" s="0">
-        <v>0.4189201295375824</v>
+        <v>0.33042618632316589</v>
       </c>
       <c r="CO6" s="0">
-        <v>0.4166463315486908</v>
+        <v>0.36358898878097534</v>
       </c>
       <c r="CP6" s="0">
-        <v>0.37699523568153381</v>
+        <v>0.3077654242515564</v>
       </c>
       <c r="CQ6" s="0">
-        <v>0.330870121717453</v>
+        <v>0.31142115592956543</v>
       </c>
       <c r="CR6" s="0">
-        <v>0.36745601892471313</v>
+        <v>0.34222549200057983</v>
       </c>
       <c r="CS6" s="0">
-        <v>0.34953635931015015</v>
+        <v>0.34262892603874207</v>
       </c>
       <c r="CT6" s="0">
-        <v>0.35663866996765137</v>
+        <v>0.31779357790946961</v>
       </c>
       <c r="CU6" s="0">
-        <v>0.37928229570388794</v>
+        <v>0.39028236269950867</v>
       </c>
       <c r="CV6" s="0">
-        <v>0.35101714730262756</v>
+        <v>0.35056298971176147</v>
       </c>
       <c r="CW6" s="0">
-        <v>0.38314616680145264</v>
+        <v>0.32482519745826721</v>
       </c>
       <c r="CX6" s="0">
-        <v>0.291391521692276</v>
+        <v>0.3173765242099762</v>
       </c>
       <c r="CY6" s="0">
-        <v>0.2979469895362854</v>
+        <v>0.29654344916343689</v>
       </c>
       <c r="CZ6" s="0">
-        <v>0.36537623405456543</v>
+        <v>0.31044507026672363</v>
       </c>
       <c r="DA6" s="0">
-        <v>0.30040976405143738</v>
+        <v>0.36382207274436951</v>
       </c>
       <c r="DB6" s="0">
-        <v>0.39783629775047302</v>
+        <v>0.39721301198005676</v>
       </c>
       <c r="DC6" s="0">
-        <v>0.34537467360496521</v>
+        <v>0.36089888215065003</v>
       </c>
       <c r="DD6" s="0">
-        <v>0.29026052355766296</v>
+        <v>0.3080420196056366</v>
       </c>
       <c r="DE6" s="0">
-        <v>0.25335374474525452</v>
+        <v>0.30622199177742004</v>
       </c>
       <c r="DF6" s="0">
-        <v>0.39120391011238098</v>
+        <v>0.4026549756526947</v>
       </c>
       <c r="DG6" s="0">
-        <v>0.40705138444900513</v>
+        <v>0.36152142286300659</v>
       </c>
       <c r="DH6" s="0">
-        <v>0.36346852779388428</v>
+        <v>0.40623739361763001</v>
       </c>
       <c r="DI6" s="0">
-        <v>0.33994853496551514</v>
+        <v>0.34739750623703003</v>
       </c>
       <c r="DJ6" s="0">
-        <v>0.30669137835502625</v>
+        <v>0.34276947379112244</v>
       </c>
       <c r="DK6" s="0">
-        <v>0.33912625908851624</v>
+        <v>0.37958231568336487</v>
       </c>
       <c r="DL6" s="0">
-        <v>0.25843116641044617</v>
+        <v>0.26215445995330811</v>
       </c>
       <c r="DM6" s="0">
-        <v>0.31397750973701477</v>
+        <v>0.33433777093887329</v>
       </c>
       <c r="DN6" s="0">
-        <v>0.41135892271995544</v>
+        <v>0.41761168837547302</v>
       </c>
       <c r="DO6" s="0">
-        <v>0.37884002923965454</v>
+        <v>0.38727861642837524</v>
       </c>
       <c r="DP6" s="0">
-        <v>0.34740501642227173</v>
+        <v>0.31562608480453491</v>
       </c>
       <c r="DQ6" s="0">
-        <v>0.34938853979110718</v>
+        <v>0.31884235143661499</v>
       </c>
       <c r="DR6" s="0">
-        <v>0.28784427046775818</v>
+        <v>0.30137699842453003</v>
       </c>
       <c r="DS6" s="0">
-        <v>0.27156639099121094</v>
+        <v>0.34667867422103882</v>
       </c>
     </row>
     <row r="7">
@@ -2882,364 +2883,364 @@
         <v>28</v>
       </c>
       <c r="D7" s="0">
-        <v>0.21508455276489258</v>
+        <v>0.41134318709373474</v>
       </c>
       <c r="E7" s="0">
-        <v>0.20079109072685242</v>
+        <v>0.39781478047370911</v>
       </c>
       <c r="F7" s="0">
-        <v>0.21478359401226044</v>
+        <v>0.41162207722663879</v>
       </c>
       <c r="G7" s="0">
-        <v>0.19333970546722412</v>
+        <v>0.39341038465499878</v>
       </c>
       <c r="H7" s="0">
-        <v>0.19825091958045959</v>
+        <v>0.38212031126022339</v>
       </c>
       <c r="I7" s="0">
-        <v>0.19439339637756348</v>
+        <v>0.40443465113639832</v>
       </c>
       <c r="J7" s="0">
-        <v>0.19725105166435242</v>
+        <v>0.39237546920776367</v>
       </c>
       <c r="K7" s="0">
-        <v>0.16782233119010925</v>
+        <v>0.3732178807258606</v>
       </c>
       <c r="L7" s="0">
-        <v>0.21549741923809052</v>
+        <v>0.39629015326499939</v>
       </c>
       <c r="M7" s="0">
-        <v>0.18588215112686157</v>
+        <v>0.38673138618469238</v>
       </c>
       <c r="N7" s="0">
-        <v>0.27271121740341187</v>
+        <v>0.47247248888015747</v>
       </c>
       <c r="O7" s="0">
-        <v>0.24416749179363251</v>
+        <v>0.45522496104240417</v>
       </c>
       <c r="P7" s="0">
-        <v>0.16017313301563263</v>
+        <v>0.35901397466659546</v>
       </c>
       <c r="Q7" s="0">
-        <v>0.21276821196079254</v>
+        <v>0.40342804789543152</v>
       </c>
       <c r="R7" s="0">
-        <v>0.22882631421089172</v>
+        <v>0.43074160814285278</v>
       </c>
       <c r="S7" s="0">
-        <v>0.24076785147190094</v>
+        <v>0.44057327508926392</v>
       </c>
       <c r="T7" s="0">
-        <v>0.16065272688865662</v>
+        <v>0.36510747671127319</v>
       </c>
       <c r="U7" s="0">
-        <v>0.16346094012260437</v>
+        <v>0.36951330304145813</v>
       </c>
       <c r="V7" s="0">
-        <v>0.22046755254268646</v>
+        <v>0.42096906900405884</v>
       </c>
       <c r="W7" s="0">
-        <v>0.19013978540897369</v>
+        <v>0.39721158146858215</v>
       </c>
       <c r="X7" s="0">
-        <v>0.37070608139038086</v>
+        <v>0.34313356876373291</v>
       </c>
       <c r="Y7" s="0">
-        <v>0.35610833764076233</v>
+        <v>0.37290331721305847</v>
       </c>
       <c r="Z7" s="0">
-        <v>0.31399461627006531</v>
+        <v>0.31441062688827515</v>
       </c>
       <c r="AA7" s="0">
-        <v>0.33841800689697266</v>
+        <v>0.38800573348999023</v>
       </c>
       <c r="AB7" s="0">
-        <v>0.34231212735176086</v>
+        <v>0.33516892790794373</v>
       </c>
       <c r="AC7" s="0">
-        <v>0.3412138819694519</v>
+        <v>0.27832266688346863</v>
       </c>
       <c r="AD7" s="0">
-        <v>0.32609140872955322</v>
+        <v>0.30310282111167908</v>
       </c>
       <c r="AE7" s="0">
-        <v>0.34352874755859375</v>
+        <v>0.28649422526359558</v>
       </c>
       <c r="AF7" s="0">
-        <v>0.36533436179161072</v>
+        <v>0.27465754747390747</v>
       </c>
       <c r="AG7" s="0">
-        <v>0.30395281314849854</v>
+        <v>0.3052544891834259</v>
       </c>
       <c r="AH7" s="0">
-        <v>0.4128149151802063</v>
+        <v>0.37025627493858337</v>
       </c>
       <c r="AI7" s="0">
-        <v>0.30690810084342957</v>
+        <v>0.3146403431892395</v>
       </c>
       <c r="AJ7" s="0">
-        <v>0.32462692260742188</v>
+        <v>0.35235729813575745</v>
       </c>
       <c r="AK7" s="0">
-        <v>0.3273487389087677</v>
+        <v>0.27666288614273071</v>
       </c>
       <c r="AL7" s="0">
-        <v>0.34717881679534912</v>
+        <v>0.3452286422252655</v>
       </c>
       <c r="AM7" s="0">
-        <v>0.41044369339942932</v>
+        <v>0.27737998962402344</v>
       </c>
       <c r="AN7" s="0">
-        <v>0.36100322008132935</v>
+        <v>0.3263474702835083</v>
       </c>
       <c r="AO7" s="0">
-        <v>0.33188122510910034</v>
+        <v>0.30449840426445007</v>
       </c>
       <c r="AP7" s="0">
-        <v>0.40581715106964111</v>
+        <v>0.31745076179504395</v>
       </c>
       <c r="AQ7" s="0">
-        <v>0.2797413170337677</v>
+        <v>0.2876594066619873</v>
       </c>
       <c r="AR7" s="0">
-        <v>0.32315528392791748</v>
+        <v>0.24699436128139496</v>
       </c>
       <c r="AS7" s="0">
-        <v>0.38875877857208252</v>
+        <v>0.26639869809150696</v>
       </c>
       <c r="AT7" s="0">
-        <v>0.35729494690895081</v>
+        <v>0.31171911954879761</v>
       </c>
       <c r="AU7" s="0">
-        <v>0.2963835597038269</v>
+        <v>0.34499800205230713</v>
       </c>
       <c r="AV7" s="0">
-        <v>0.32672899961471558</v>
+        <v>0.29720950126647949</v>
       </c>
       <c r="AW7" s="0">
-        <v>0.31273734569549561</v>
+        <v>0.29879042506217957</v>
       </c>
       <c r="AX7" s="0">
-        <v>0.34086024761199951</v>
+        <v>0.33449757099151611</v>
       </c>
       <c r="AY7" s="0">
-        <v>0.39113029837608337</v>
+        <v>0.38914525508880615</v>
       </c>
       <c r="AZ7" s="0">
-        <v>0.39021223783493042</v>
+        <v>0.3037247359752655</v>
       </c>
       <c r="BA7" s="0">
-        <v>0.29782873392105103</v>
+        <v>0.33859926462173462</v>
       </c>
       <c r="BB7" s="0">
-        <v>0.32121109962463379</v>
+        <v>0.31614178419113159</v>
       </c>
       <c r="BC7" s="0">
-        <v>0.35990384221076965</v>
+        <v>0.32200697064399719</v>
       </c>
       <c r="BD7" s="0">
-        <v>0.31869161128997803</v>
+        <v>0.3414803147315979</v>
       </c>
       <c r="BE7" s="0">
-        <v>0.30789855122566223</v>
+        <v>0.31250953674316406</v>
       </c>
       <c r="BF7" s="0">
-        <v>0.31582203507423401</v>
+        <v>0.39146265387535095</v>
       </c>
       <c r="BG7" s="0">
-        <v>0.39687666296958923</v>
+        <v>0.39265850186347962</v>
       </c>
       <c r="BH7" s="0">
-        <v>0.3553413450717926</v>
+        <v>0.33751934766769409</v>
       </c>
       <c r="BI7" s="0">
-        <v>0.34751591086387634</v>
+        <v>0.34033873677253723</v>
       </c>
       <c r="BJ7" s="0">
-        <v>0.32495465874671936</v>
+        <v>0.27640673518180847</v>
       </c>
       <c r="BK7" s="0">
-        <v>0.38716846704483032</v>
+        <v>0.39865979552268982</v>
       </c>
       <c r="BL7" s="0">
-        <v>0.34377285838127136</v>
+        <v>0.33855882287025452</v>
       </c>
       <c r="BM7" s="0">
-        <v>0.36910459399223328</v>
+        <v>0.326261967420578</v>
       </c>
       <c r="BN7" s="0">
-        <v>0.31977510452270508</v>
+        <v>0.34829628467559814</v>
       </c>
       <c r="BO7" s="0">
-        <v>0.38743332028388977</v>
+        <v>0.32275828719139099</v>
       </c>
       <c r="BP7" s="0">
-        <v>0.35150381922721863</v>
+        <v>0.33522197604179382</v>
       </c>
       <c r="BQ7" s="0">
-        <v>0.37441697716712952</v>
+        <v>0.31304898858070374</v>
       </c>
       <c r="BR7" s="0">
-        <v>0.36148726940155029</v>
+        <v>0.30621388554573059</v>
       </c>
       <c r="BS7" s="0">
-        <v>0.32595729827880859</v>
+        <v>0.3176800012588501</v>
       </c>
       <c r="BT7" s="0">
-        <v>0.39232710003852844</v>
+        <v>0.29943129420280457</v>
       </c>
       <c r="BU7" s="0">
-        <v>0.36077752709388733</v>
+        <v>0.3737930953502655</v>
       </c>
       <c r="BV7" s="0">
-        <v>0.38952437043190002</v>
+        <v>0.36449801921844482</v>
       </c>
       <c r="BW7" s="0">
-        <v>0.3613646924495697</v>
+        <v>0.32095903158187866</v>
       </c>
       <c r="BX7" s="0">
-        <v>0.39476203918457031</v>
+        <v>0.36476230621337891</v>
       </c>
       <c r="BY7" s="0">
-        <v>0.3827843964099884</v>
+        <v>0.33751818537712097</v>
       </c>
       <c r="BZ7" s="0">
-        <v>0.40778064727783203</v>
+        <v>0.37319669127464294</v>
       </c>
       <c r="CA7" s="0">
-        <v>0.40497121214866638</v>
+        <v>0.31742143630981445</v>
       </c>
       <c r="CB7" s="0">
-        <v>0.3633064329624176</v>
+        <v>0.3896666169166565</v>
       </c>
       <c r="CC7" s="0">
-        <v>0.3609822690486908</v>
+        <v>0.34682431817054749</v>
       </c>
       <c r="CD7" s="0">
-        <v>0.3683074414730072</v>
+        <v>0.29114723205566406</v>
       </c>
       <c r="CE7" s="0">
-        <v>0.35554343461990356</v>
+        <v>0.33566576242446899</v>
       </c>
       <c r="CF7" s="0">
-        <v>0.3655954897403717</v>
+        <v>0.36636844277381897</v>
       </c>
       <c r="CG7" s="0">
-        <v>0.45086327195167542</v>
+        <v>0.36043685674667358</v>
       </c>
       <c r="CH7" s="0">
-        <v>0.30572822690010071</v>
+        <v>0.25841021537780762</v>
       </c>
       <c r="CI7" s="0">
-        <v>0.34589236974716187</v>
+        <v>0.24507388472557068</v>
       </c>
       <c r="CJ7" s="0">
-        <v>0.3832913339138031</v>
+        <v>0.3081335723400116</v>
       </c>
       <c r="CK7" s="0">
-        <v>0.4261203408241272</v>
+        <v>0.30800780653953552</v>
       </c>
       <c r="CL7" s="0">
-        <v>0.35888853669166565</v>
+        <v>0.32664167881011963</v>
       </c>
       <c r="CM7" s="0">
-        <v>0.3461717963218689</v>
+        <v>0.32027092576026917</v>
       </c>
       <c r="CN7" s="0">
-        <v>0.37129071354866028</v>
+        <v>0.30587548017501831</v>
       </c>
       <c r="CO7" s="0">
-        <v>0.36414933204650879</v>
+        <v>0.32272636890411377</v>
       </c>
       <c r="CP7" s="0">
-        <v>0.32058426737785339</v>
+        <v>0.32894545793533325</v>
       </c>
       <c r="CQ7" s="0">
-        <v>0.34185269474983215</v>
+        <v>0.34100097417831421</v>
       </c>
       <c r="CR7" s="0">
-        <v>0.36933761835098267</v>
+        <v>0.3383491039276123</v>
       </c>
       <c r="CS7" s="0">
-        <v>0.33912071585655212</v>
+        <v>0.30577355623245239</v>
       </c>
       <c r="CT7" s="0">
-        <v>0.41326940059661865</v>
+        <v>0.38755017518997192</v>
       </c>
       <c r="CU7" s="0">
-        <v>0.30939170718193054</v>
+        <v>0.353282630443573</v>
       </c>
       <c r="CV7" s="0">
-        <v>0.33759593963623047</v>
+        <v>0.32629355788230896</v>
       </c>
       <c r="CW7" s="0">
-        <v>0.34000015258789062</v>
+        <v>0.32248678803443909</v>
       </c>
       <c r="CX7" s="0">
-        <v>0.26004528999328613</v>
+        <v>0.27602848410606384</v>
       </c>
       <c r="CY7" s="0">
-        <v>0.29195284843444824</v>
+        <v>0.27817603945732117</v>
       </c>
       <c r="CZ7" s="0">
-        <v>0.33345386385917664</v>
+        <v>0.32278856635093689</v>
       </c>
       <c r="DA7" s="0">
-        <v>0.30498096346855164</v>
+        <v>0.32535484433174133</v>
       </c>
       <c r="DB7" s="0">
-        <v>0.40204384922981262</v>
+        <v>0.32877835631370545</v>
       </c>
       <c r="DC7" s="0">
-        <v>0.37271192669868469</v>
+        <v>0.2739492654800415</v>
       </c>
       <c r="DD7" s="0">
-        <v>0.33412635326385498</v>
+        <v>0.2606695294380188</v>
       </c>
       <c r="DE7" s="0">
-        <v>0.36872491240501404</v>
+        <v>0.30072924494743347</v>
       </c>
       <c r="DF7" s="0">
-        <v>0.42963370680809021</v>
+        <v>0.33201444149017334</v>
       </c>
       <c r="DG7" s="0">
-        <v>0.36277922987937927</v>
+        <v>0.39183938503265381</v>
       </c>
       <c r="DH7" s="0">
-        <v>0.41650509834289551</v>
+        <v>0.34736123681068421</v>
       </c>
       <c r="DI7" s="0">
-        <v>0.38546645641326904</v>
+        <v>0.33408120274543762</v>
       </c>
       <c r="DJ7" s="0">
-        <v>0.36159244179725647</v>
+        <v>0.26709741353988647</v>
       </c>
       <c r="DK7" s="0">
-        <v>0.32659220695495605</v>
+        <v>0.29434612393379212</v>
       </c>
       <c r="DL7" s="0">
-        <v>0.18250863254070282</v>
+        <v>0.17694984376430512</v>
       </c>
       <c r="DM7" s="0">
-        <v>0.33834132552146912</v>
+        <v>0.33411523699760437</v>
       </c>
       <c r="DN7" s="0">
-        <v>0.45061317086219788</v>
+        <v>0.3500787615776062</v>
       </c>
       <c r="DO7" s="0">
-        <v>0.41689556837081909</v>
+        <v>0.41124564409255981</v>
       </c>
       <c r="DP7" s="0">
-        <v>0.3126855194568634</v>
+        <v>0.31440770626068115</v>
       </c>
       <c r="DQ7" s="0">
-        <v>0.31408441066741943</v>
+        <v>0.27628806233406067</v>
       </c>
       <c r="DR7" s="0">
-        <v>0.31346297264099121</v>
+        <v>0.31089624762535095</v>
       </c>
       <c r="DS7" s="0">
-        <v>0.34831711649894714</v>
+        <v>0.32657349109649658</v>
       </c>
     </row>
     <row r="8">
@@ -3253,364 +3254,364 @@
         <v>29</v>
       </c>
       <c r="D8" s="0">
-        <v>0.35312262177467346</v>
+        <v>0.27859726548194885</v>
       </c>
       <c r="E8" s="0">
-        <v>0.3369651734828949</v>
+        <v>0.25098270177841187</v>
       </c>
       <c r="F8" s="0">
-        <v>0.36507609486579895</v>
+        <v>0.26330432295799255</v>
       </c>
       <c r="G8" s="0">
-        <v>0.32212239503860474</v>
+        <v>0.26512694358825684</v>
       </c>
       <c r="H8" s="0">
-        <v>0.31948244571685791</v>
+        <v>0.26386857032775879</v>
       </c>
       <c r="I8" s="0">
-        <v>0.33794930577278137</v>
+        <v>0.2480793297290802</v>
       </c>
       <c r="J8" s="0">
-        <v>0.316099613904953</v>
+        <v>0.24695529043674469</v>
       </c>
       <c r="K8" s="0">
-        <v>0.31349539756774902</v>
+        <v>0.24096184968948364</v>
       </c>
       <c r="L8" s="0">
-        <v>0.34175762534141541</v>
+        <v>0.27715674042701721</v>
       </c>
       <c r="M8" s="0">
-        <v>0.3233000636100769</v>
+        <v>0.24134768545627594</v>
       </c>
       <c r="N8" s="0">
-        <v>0.41512972116470337</v>
+        <v>0.31936684250831604</v>
       </c>
       <c r="O8" s="0">
-        <v>0.37460547685623169</v>
+        <v>0.30467444658279419</v>
       </c>
       <c r="P8" s="0">
-        <v>0.30330857634544373</v>
+        <v>0.26172378659248352</v>
       </c>
       <c r="Q8" s="0">
-        <v>0.32351842522621155</v>
+        <v>0.27505549788475037</v>
       </c>
       <c r="R8" s="0">
-        <v>0.36666092276573181</v>
+        <v>0.29149466753005982</v>
       </c>
       <c r="S8" s="0">
-        <v>0.39537739753723145</v>
+        <v>0.31925520300865173</v>
       </c>
       <c r="T8" s="0">
-        <v>0.30608263611793518</v>
+        <v>0.21881334483623505</v>
       </c>
       <c r="U8" s="0">
-        <v>0.29164668917655945</v>
+        <v>0.22194758057594299</v>
       </c>
       <c r="V8" s="0">
-        <v>0.35251075029373169</v>
+        <v>0.29458484053611755</v>
       </c>
       <c r="W8" s="0">
-        <v>0.34075012803077698</v>
+        <v>0.26679506897926331</v>
       </c>
       <c r="X8" s="0">
-        <v>0.39137506484985352</v>
+        <v>0.37555348873138428</v>
       </c>
       <c r="Y8" s="0">
-        <v>0.40614259243011475</v>
+        <v>0.31589028239250183</v>
       </c>
       <c r="Z8" s="0">
-        <v>0.35653340816497803</v>
+        <v>0.33909222483634949</v>
       </c>
       <c r="AA8" s="0">
-        <v>0.41998001933097839</v>
+        <v>0.33517619967460632</v>
       </c>
       <c r="AB8" s="0">
-        <v>0.39610287547111511</v>
+        <v>0.33123809099197388</v>
       </c>
       <c r="AC8" s="0">
-        <v>0.43291160464286804</v>
+        <v>0.3385668694972992</v>
       </c>
       <c r="AD8" s="0">
-        <v>0.32366880774497986</v>
+        <v>0.33073532581329346</v>
       </c>
       <c r="AE8" s="0">
-        <v>0.40705946087837219</v>
+        <v>0.28992798924446106</v>
       </c>
       <c r="AF8" s="0">
-        <v>0.32058447599411011</v>
+        <v>0.27208307385444641</v>
       </c>
       <c r="AG8" s="0">
-        <v>0.31367078423500061</v>
+        <v>0.3072284460067749</v>
       </c>
       <c r="AH8" s="0">
-        <v>0.43112829327583313</v>
+        <v>0.40390676259994507</v>
       </c>
       <c r="AI8" s="0">
-        <v>0.32248842716217041</v>
+        <v>0.284709632396698</v>
       </c>
       <c r="AJ8" s="0">
-        <v>0.42687115073204041</v>
+        <v>0.33510744571685791</v>
       </c>
       <c r="AK8" s="0">
-        <v>0.3542233407497406</v>
+        <v>0.3107534646987915</v>
       </c>
       <c r="AL8" s="0">
-        <v>0.388194739818573</v>
+        <v>0.31797093152999878</v>
       </c>
       <c r="AM8" s="0">
-        <v>0.36743050813674927</v>
+        <v>0.36314296722412109</v>
       </c>
       <c r="AN8" s="0">
-        <v>0.37845450639724731</v>
+        <v>0.30797478556632996</v>
       </c>
       <c r="AO8" s="0">
-        <v>0.38481691479682922</v>
+        <v>0.32582268118858337</v>
       </c>
       <c r="AP8" s="0">
-        <v>0.34743580222129822</v>
+        <v>0.36261069774627686</v>
       </c>
       <c r="AQ8" s="0">
-        <v>0.35874560475349426</v>
+        <v>0.30719354748725891</v>
       </c>
       <c r="AR8" s="0">
-        <v>0.32938450574874878</v>
+        <v>0.27161747217178345</v>
       </c>
       <c r="AS8" s="0">
-        <v>0.3932744562625885</v>
+        <v>0.32310888171195984</v>
       </c>
       <c r="AT8" s="0">
-        <v>0.33874627947807312</v>
+        <v>0.35994726419448853</v>
       </c>
       <c r="AU8" s="0">
-        <v>0.3541337251663208</v>
+        <v>0.28510844707489014</v>
       </c>
       <c r="AV8" s="0">
-        <v>0.39321848750114441</v>
+        <v>0.26981106400489807</v>
       </c>
       <c r="AW8" s="0">
-        <v>0.36935535073280334</v>
+        <v>0.31224727630615234</v>
       </c>
       <c r="AX8" s="0">
-        <v>0.38808104395866394</v>
+        <v>0.318797767162323</v>
       </c>
       <c r="AY8" s="0">
-        <v>0.34585833549499512</v>
+        <v>0.33099612593650818</v>
       </c>
       <c r="AZ8" s="0">
-        <v>0.36846491694450378</v>
+        <v>0.32803899049758911</v>
       </c>
       <c r="BA8" s="0">
-        <v>0.35206270217895508</v>
+        <v>0.3207264244556427</v>
       </c>
       <c r="BB8" s="0">
-        <v>0.35523974895477295</v>
+        <v>0.2929796576499939</v>
       </c>
       <c r="BC8" s="0">
-        <v>0.37374591827392578</v>
+        <v>0.33951237797737122</v>
       </c>
       <c r="BD8" s="0">
-        <v>0.38099595904350281</v>
+        <v>0.31431663036346436</v>
       </c>
       <c r="BE8" s="0">
-        <v>0.37368503212928772</v>
+        <v>0.33813482522964478</v>
       </c>
       <c r="BF8" s="0">
-        <v>0.39495855569839478</v>
+        <v>0.33923092484474182</v>
       </c>
       <c r="BG8" s="0">
-        <v>0.43637052178382874</v>
+        <v>0.34605711698532104</v>
       </c>
       <c r="BH8" s="0">
-        <v>0.38979983329772949</v>
+        <v>0.31139111518859863</v>
       </c>
       <c r="BI8" s="0">
-        <v>0.3748127818107605</v>
+        <v>0.32017698884010315</v>
       </c>
       <c r="BJ8" s="0">
-        <v>0.37858909368515015</v>
+        <v>0.33544266223907471</v>
       </c>
       <c r="BK8" s="0">
-        <v>0.34655222296714783</v>
+        <v>0.3517737090587616</v>
       </c>
       <c r="BL8" s="0">
-        <v>0.37125396728515625</v>
+        <v>0.36528250575065613</v>
       </c>
       <c r="BM8" s="0">
-        <v>0.4095720648765564</v>
+        <v>0.35339698195457459</v>
       </c>
       <c r="BN8" s="0">
-        <v>0.38768601417541504</v>
+        <v>0.34433683753013611</v>
       </c>
       <c r="BO8" s="0">
-        <v>0.33538952469825745</v>
+        <v>0.34746053814888</v>
       </c>
       <c r="BP8" s="0">
-        <v>0.39731138944625854</v>
+        <v>0.33327758312225342</v>
       </c>
       <c r="BQ8" s="0">
-        <v>0.4251067042350769</v>
+        <v>0.36084458231925964</v>
       </c>
       <c r="BR8" s="0">
-        <v>0.38864710927009583</v>
+        <v>0.35439515113830566</v>
       </c>
       <c r="BS8" s="0">
-        <v>0.35177373886108398</v>
+        <v>0.33649903535842896</v>
       </c>
       <c r="BT8" s="0">
-        <v>0.32833296060562134</v>
+        <v>0.30184534192085266</v>
       </c>
       <c r="BU8" s="0">
-        <v>0.38696298003196716</v>
+        <v>0.39732736349105835</v>
       </c>
       <c r="BV8" s="0">
-        <v>0.42005085945129395</v>
+        <v>0.42310333251953125</v>
       </c>
       <c r="BW8" s="0">
-        <v>0.44078508019447327</v>
+        <v>0.35510066151618958</v>
       </c>
       <c r="BX8" s="0">
-        <v>0.40318509936332703</v>
+        <v>0.32092219591140747</v>
       </c>
       <c r="BY8" s="0">
-        <v>0.44599714875221252</v>
+        <v>0.39196884632110596</v>
       </c>
       <c r="BZ8" s="0">
-        <v>0.40963637828826904</v>
+        <v>0.36603814363479614</v>
       </c>
       <c r="CA8" s="0">
-        <v>0.35359302163124084</v>
+        <v>0.33771637082099915</v>
       </c>
       <c r="CB8" s="0">
-        <v>0.37664592266082764</v>
+        <v>0.38804036378860474</v>
       </c>
       <c r="CC8" s="0">
-        <v>0.42354699969291687</v>
+        <v>0.34427827596664429</v>
       </c>
       <c r="CD8" s="0">
-        <v>0.31657907366752625</v>
+        <v>0.30800643563270569</v>
       </c>
       <c r="CE8" s="0">
-        <v>0.38811156153678894</v>
+        <v>0.35358452796936035</v>
       </c>
       <c r="CF8" s="0">
-        <v>0.38530728220939636</v>
+        <v>0.34787219762802124</v>
       </c>
       <c r="CG8" s="0">
-        <v>0.40642598271369934</v>
+        <v>0.3936724066734314</v>
       </c>
       <c r="CH8" s="0">
-        <v>0.35431939363479614</v>
+        <v>0.24146182835102081</v>
       </c>
       <c r="CI8" s="0">
-        <v>0.33425983786582947</v>
+        <v>0.28464698791503906</v>
       </c>
       <c r="CJ8" s="0">
-        <v>0.37663134932518005</v>
+        <v>0.36206960678100586</v>
       </c>
       <c r="CK8" s="0">
-        <v>0.4392516016960144</v>
+        <v>0.39594629406929016</v>
       </c>
       <c r="CL8" s="0">
-        <v>0.34817403554916382</v>
+        <v>0.37679421901702881</v>
       </c>
       <c r="CM8" s="0">
-        <v>0.37546688318252563</v>
+        <v>0.28927221894264221</v>
       </c>
       <c r="CN8" s="0">
-        <v>0.41722983121871948</v>
+        <v>0.35231363773345947</v>
       </c>
       <c r="CO8" s="0">
-        <v>0.41274404525756836</v>
+        <v>0.34758752584457397</v>
       </c>
       <c r="CP8" s="0">
-        <v>0.30212727189064026</v>
+        <v>0.36106070876121521</v>
       </c>
       <c r="CQ8" s="0">
-        <v>0.38548526167869568</v>
+        <v>0.31033036112785339</v>
       </c>
       <c r="CR8" s="0">
-        <v>0.35395044088363647</v>
+        <v>0.33224266767501831</v>
       </c>
       <c r="CS8" s="0">
-        <v>0.42931488156318665</v>
+        <v>0.35206812620162964</v>
       </c>
       <c r="CT8" s="0">
-        <v>0.38278675079345703</v>
+        <v>0.38562718033790588</v>
       </c>
       <c r="CU8" s="0">
-        <v>0.39426341652870178</v>
+        <v>0.32080176472663879</v>
       </c>
       <c r="CV8" s="0">
-        <v>0.34266453981399536</v>
+        <v>0.3198426365852356</v>
       </c>
       <c r="CW8" s="0">
-        <v>0.38672912120819092</v>
+        <v>0.42175179719924927</v>
       </c>
       <c r="CX8" s="0">
-        <v>0.39302125573158264</v>
+        <v>0.32911169528961182</v>
       </c>
       <c r="CY8" s="0">
-        <v>0.26208090782165527</v>
+        <v>0.34936654567718506</v>
       </c>
       <c r="CZ8" s="0">
-        <v>0.35892665386199951</v>
+        <v>0.35127013921737671</v>
       </c>
       <c r="DA8" s="0">
-        <v>0.35137060284614563</v>
+        <v>0.32049715518951416</v>
       </c>
       <c r="DB8" s="0">
-        <v>0.38257536292076111</v>
+        <v>0.31399661302566528</v>
       </c>
       <c r="DC8" s="0">
-        <v>0.42892041802406311</v>
+        <v>0.29434648156166077</v>
       </c>
       <c r="DD8" s="0">
-        <v>0.34016519784927368</v>
+        <v>0.31499308347702026</v>
       </c>
       <c r="DE8" s="0">
-        <v>0.27876034379005432</v>
+        <v>0.28213903307914734</v>
       </c>
       <c r="DF8" s="0">
-        <v>0.35260540246963501</v>
+        <v>0.33617222309112549</v>
       </c>
       <c r="DG8" s="0">
-        <v>0.42585843801498413</v>
+        <v>0.36017420887947083</v>
       </c>
       <c r="DH8" s="0">
-        <v>0.37566924095153809</v>
+        <v>0.37324458360671997</v>
       </c>
       <c r="DI8" s="0">
-        <v>0.37261620163917542</v>
+        <v>0.37795901298522949</v>
       </c>
       <c r="DJ8" s="0">
-        <v>0.37746366858482361</v>
+        <v>0.38983434438705444</v>
       </c>
       <c r="DK8" s="0">
-        <v>0.3503328263759613</v>
+        <v>0.32684493064880371</v>
       </c>
       <c r="DL8" s="0">
-        <v>0.24909599125385284</v>
+        <v>0.26890724897384644</v>
       </c>
       <c r="DM8" s="0">
-        <v>0.3785710334777832</v>
+        <v>0.36838456988334656</v>
       </c>
       <c r="DN8" s="0">
-        <v>0.42111718654632568</v>
+        <v>0.40216606855392456</v>
       </c>
       <c r="DO8" s="0">
-        <v>0.37912791967391968</v>
+        <v>0.36569789052009583</v>
       </c>
       <c r="DP8" s="0">
-        <v>0.29662194848060608</v>
+        <v>0.29651263356208801</v>
       </c>
       <c r="DQ8" s="0">
-        <v>0.36302945017814636</v>
+        <v>0.37136238813400269</v>
       </c>
       <c r="DR8" s="0">
-        <v>0.36503320932388306</v>
+        <v>0.29176118969917297</v>
       </c>
       <c r="DS8" s="0">
-        <v>0.33636212348937988</v>
+        <v>0.35218840837478638</v>
       </c>
     </row>
     <row r="9">
@@ -3624,364 +3625,364 @@
         <v>30</v>
       </c>
       <c r="D9" s="0">
-        <v>0.31917697191238403</v>
+        <v>0.33396154642105103</v>
       </c>
       <c r="E9" s="0">
-        <v>0.32300981879234314</v>
+        <v>0.33332952857017517</v>
       </c>
       <c r="F9" s="0">
-        <v>0.3254123330116272</v>
+        <v>0.33299121260643005</v>
       </c>
       <c r="G9" s="0">
-        <v>0.29226472973823547</v>
+        <v>0.30597454309463501</v>
       </c>
       <c r="H9" s="0">
-        <v>0.28921723365783691</v>
+        <v>0.31814748048782349</v>
       </c>
       <c r="I9" s="0">
-        <v>0.31750112771987915</v>
+        <v>0.3236047625541687</v>
       </c>
       <c r="J9" s="0">
-        <v>0.31539201736450195</v>
+        <v>0.30626463890075684</v>
       </c>
       <c r="K9" s="0">
-        <v>0.29475992918014526</v>
+        <v>0.31568339467048645</v>
       </c>
       <c r="L9" s="0">
-        <v>0.34545290470123291</v>
+        <v>0.33113256096839905</v>
       </c>
       <c r="M9" s="0">
-        <v>0.30030983686447144</v>
+        <v>0.30640998482704163</v>
       </c>
       <c r="N9" s="0">
-        <v>0.41252097487449646</v>
+        <v>0.40966916084289551</v>
       </c>
       <c r="O9" s="0">
-        <v>0.35855618119239807</v>
+        <v>0.35014447569847107</v>
       </c>
       <c r="P9" s="0">
-        <v>0.29170641303062439</v>
+        <v>0.30193907022476196</v>
       </c>
       <c r="Q9" s="0">
-        <v>0.323415607213974</v>
+        <v>0.32635745406150818</v>
       </c>
       <c r="R9" s="0">
-        <v>0.3535134494304657</v>
+        <v>0.34617045521736145</v>
       </c>
       <c r="S9" s="0">
-        <v>0.37457013130187988</v>
+        <v>0.35859820246696472</v>
       </c>
       <c r="T9" s="0">
-        <v>0.28964713215827942</v>
+        <v>0.29506182670593262</v>
       </c>
       <c r="U9" s="0">
-        <v>0.29061725735664368</v>
+        <v>0.28991946578025818</v>
       </c>
       <c r="V9" s="0">
-        <v>0.35546702146530151</v>
+        <v>0.34254398941993713</v>
       </c>
       <c r="W9" s="0">
-        <v>0.3238970935344696</v>
+        <v>0.33043399453163147</v>
       </c>
       <c r="X9" s="0">
-        <v>0.32413211464881897</v>
+        <v>0.28380516171455383</v>
       </c>
       <c r="Y9" s="0">
-        <v>0.30773067474365234</v>
+        <v>0.31623491644859314</v>
       </c>
       <c r="Z9" s="0">
-        <v>0.34524890780448914</v>
+        <v>0.34520852565765381</v>
       </c>
       <c r="AA9" s="0">
-        <v>0.32338935136795044</v>
+        <v>0.30900192260742188</v>
       </c>
       <c r="AB9" s="0">
-        <v>0.32210850715637207</v>
+        <v>0.31439954042434692</v>
       </c>
       <c r="AC9" s="0">
-        <v>0.34892287850379944</v>
+        <v>0.32549551129341126</v>
       </c>
       <c r="AD9" s="0">
-        <v>0.32468664646148682</v>
+        <v>0.28724196553230286</v>
       </c>
       <c r="AE9" s="0">
-        <v>0.25876995921134949</v>
+        <v>0.3069969117641449</v>
       </c>
       <c r="AF9" s="0">
-        <v>0.21364805102348328</v>
+        <v>0.24136950075626373</v>
       </c>
       <c r="AG9" s="0">
-        <v>0.30038005113601685</v>
+        <v>0.31286630034446716</v>
       </c>
       <c r="AH9" s="0">
-        <v>0.42581251263618469</v>
+        <v>0.35841268301010132</v>
       </c>
       <c r="AI9" s="0">
-        <v>0.2534654438495636</v>
+        <v>0.27824702858924866</v>
       </c>
       <c r="AJ9" s="0">
-        <v>0.34606754779815674</v>
+        <v>0.31794339418411255</v>
       </c>
       <c r="AK9" s="0">
-        <v>0.33726951479911804</v>
+        <v>0.31989970803260803</v>
       </c>
       <c r="AL9" s="0">
-        <v>0.3071378767490387</v>
+        <v>0.3227720856666565</v>
       </c>
       <c r="AM9" s="0">
-        <v>0.29506880044937134</v>
+        <v>0.31981605291366577</v>
       </c>
       <c r="AN9" s="0">
-        <v>0.3274172842502594</v>
+        <v>0.34046012163162232</v>
       </c>
       <c r="AO9" s="0">
-        <v>0.36498355865478516</v>
+        <v>0.31253376603126526</v>
       </c>
       <c r="AP9" s="0">
-        <v>0.31518208980560303</v>
+        <v>0.29858997464179993</v>
       </c>
       <c r="AQ9" s="0">
-        <v>0.28563964366912842</v>
+        <v>0.24757638573646545</v>
       </c>
       <c r="AR9" s="0">
-        <v>0.31122928857803345</v>
+        <v>0.33006671071052551</v>
       </c>
       <c r="AS9" s="0">
-        <v>0.31275215744972229</v>
+        <v>0.33738869428634644</v>
       </c>
       <c r="AT9" s="0">
-        <v>0.33345732092857361</v>
+        <v>0.3456328809261322</v>
       </c>
       <c r="AU9" s="0">
-        <v>0.33635962009429932</v>
+        <v>0.32074928283691406</v>
       </c>
       <c r="AV9" s="0">
-        <v>0.28114062547683716</v>
+        <v>0.34975263476371765</v>
       </c>
       <c r="AW9" s="0">
-        <v>0.32097861170768738</v>
+        <v>0.30291351675987244</v>
       </c>
       <c r="AX9" s="0">
-        <v>0.38037508726119995</v>
+        <v>0.39761999249458313</v>
       </c>
       <c r="AY9" s="0">
-        <v>0.38697192072868347</v>
+        <v>0.31863412261009216</v>
       </c>
       <c r="AZ9" s="0">
-        <v>0.34329870343208313</v>
+        <v>0.35830211639404297</v>
       </c>
       <c r="BA9" s="0">
-        <v>0.34277132153511047</v>
+        <v>0.30756378173828125</v>
       </c>
       <c r="BB9" s="0">
-        <v>0.36909011006355286</v>
+        <v>0.33933559060096741</v>
       </c>
       <c r="BC9" s="0">
-        <v>0.36994254589080811</v>
+        <v>0.30275225639343262</v>
       </c>
       <c r="BD9" s="0">
-        <v>0.29153576493263245</v>
+        <v>0.31146085262298584</v>
       </c>
       <c r="BE9" s="0">
-        <v>0.27890759706497192</v>
+        <v>0.34750157594680786</v>
       </c>
       <c r="BF9" s="0">
-        <v>0.30364707112312317</v>
+        <v>0.32683664560317993</v>
       </c>
       <c r="BG9" s="0">
-        <v>0.36056959629058838</v>
+        <v>0.37224522233009338</v>
       </c>
       <c r="BH9" s="0">
-        <v>0.34140971302986145</v>
+        <v>0.38442414999008179</v>
       </c>
       <c r="BI9" s="0">
-        <v>0.30872753262519836</v>
+        <v>0.33881282806396484</v>
       </c>
       <c r="BJ9" s="0">
-        <v>0.32961001992225647</v>
+        <v>0.32071772217750549</v>
       </c>
       <c r="BK9" s="0">
-        <v>0.38428795337677002</v>
+        <v>0.36366245150566101</v>
       </c>
       <c r="BL9" s="0">
-        <v>0.3351263701915741</v>
+        <v>0.34205973148345947</v>
       </c>
       <c r="BM9" s="0">
-        <v>0.31581881642341614</v>
+        <v>0.37238693237304688</v>
       </c>
       <c r="BN9" s="0">
-        <v>0.30469778180122375</v>
+        <v>0.39362156391143799</v>
       </c>
       <c r="BO9" s="0">
-        <v>0.3021065890789032</v>
+        <v>0.34620752930641174</v>
       </c>
       <c r="BP9" s="0">
-        <v>0.26734933257102966</v>
+        <v>0.36026319861412048</v>
       </c>
       <c r="BQ9" s="0">
-        <v>0.34541669487953186</v>
+        <v>0.33131998777389526</v>
       </c>
       <c r="BR9" s="0">
-        <v>0.35188910365104675</v>
+        <v>0.3429979681968689</v>
       </c>
       <c r="BS9" s="0">
-        <v>0.30579060316085815</v>
+        <v>0.3419700562953949</v>
       </c>
       <c r="BT9" s="0">
-        <v>0.36087504029273987</v>
+        <v>0.33448293805122375</v>
       </c>
       <c r="BU9" s="0">
-        <v>0.34146404266357422</v>
+        <v>0.36433500051498413</v>
       </c>
       <c r="BV9" s="0">
-        <v>0.37813547253608704</v>
+        <v>0.3667488694190979</v>
       </c>
       <c r="BW9" s="0">
-        <v>0.35759812593460083</v>
+        <v>0.34387624263763428</v>
       </c>
       <c r="BX9" s="0">
-        <v>0.30114671587944031</v>
+        <v>0.32926139235496521</v>
       </c>
       <c r="BY9" s="0">
-        <v>0.30379834771156311</v>
+        <v>0.38418316841125488</v>
       </c>
       <c r="BZ9" s="0">
-        <v>0.33037877082824707</v>
+        <v>0.35939887166023254</v>
       </c>
       <c r="CA9" s="0">
-        <v>0.33247223496437073</v>
+        <v>0.31443318724632263</v>
       </c>
       <c r="CB9" s="0">
-        <v>0.34919002652168274</v>
+        <v>0.33259251713752747</v>
       </c>
       <c r="CC9" s="0">
-        <v>0.35775250196456909</v>
+        <v>0.34248942136764526</v>
       </c>
       <c r="CD9" s="0">
-        <v>0.33577358722686768</v>
+        <v>0.29905387759208679</v>
       </c>
       <c r="CE9" s="0">
-        <v>0.2989385724067688</v>
+        <v>0.35876619815826416</v>
       </c>
       <c r="CF9" s="0">
-        <v>0.29656994342803955</v>
+        <v>0.32168728113174438</v>
       </c>
       <c r="CG9" s="0">
-        <v>0.34401941299438477</v>
+        <v>0.34525695443153381</v>
       </c>
       <c r="CH9" s="0">
-        <v>0.27497050166130066</v>
+        <v>0.23732228577136993</v>
       </c>
       <c r="CI9" s="0">
-        <v>0.29574620723724365</v>
+        <v>0.33290153741836548</v>
       </c>
       <c r="CJ9" s="0">
-        <v>0.35134398937225342</v>
+        <v>0.32596293091773987</v>
       </c>
       <c r="CK9" s="0">
-        <v>0.3144649863243103</v>
+        <v>0.36824262142181396</v>
       </c>
       <c r="CL9" s="0">
-        <v>0.33815494179725647</v>
+        <v>0.30932769179344177</v>
       </c>
       <c r="CM9" s="0">
-        <v>0.2774907648563385</v>
+        <v>0.28544872999191284</v>
       </c>
       <c r="CN9" s="0">
-        <v>0.35129937529563904</v>
+        <v>0.3562949001789093</v>
       </c>
       <c r="CO9" s="0">
-        <v>0.32801923155784607</v>
+        <v>0.34361234307289124</v>
       </c>
       <c r="CP9" s="0">
-        <v>0.31044945120811462</v>
+        <v>0.3610844612121582</v>
       </c>
       <c r="CQ9" s="0">
-        <v>0.29323843121528625</v>
+        <v>0.29565271735191345</v>
       </c>
       <c r="CR9" s="0">
-        <v>0.36569646000862122</v>
+        <v>0.36906805634498596</v>
       </c>
       <c r="CS9" s="0">
-        <v>0.28900867700576782</v>
+        <v>0.33263993263244629</v>
       </c>
       <c r="CT9" s="0">
-        <v>0.35733366012573242</v>
+        <v>0.29548266530036926</v>
       </c>
       <c r="CU9" s="0">
-        <v>0.2930360734462738</v>
+        <v>0.34328481554985046</v>
       </c>
       <c r="CV9" s="0">
-        <v>0.30131766200065613</v>
+        <v>0.30493456125259399</v>
       </c>
       <c r="CW9" s="0">
-        <v>0.37832382321357727</v>
+        <v>0.31865349411964417</v>
       </c>
       <c r="CX9" s="0">
-        <v>0.24927246570587158</v>
+        <v>0.27498078346252442</v>
       </c>
       <c r="CY9" s="0">
-        <v>0.34971323609352112</v>
+        <v>0.30557319521903992</v>
       </c>
       <c r="CZ9" s="0">
-        <v>0.30004125833511353</v>
+        <v>0.34273731708526611</v>
       </c>
       <c r="DA9" s="0">
-        <v>0.35668030381202698</v>
+        <v>0.2934814989566803</v>
       </c>
       <c r="DB9" s="0">
-        <v>0.30516105890274048</v>
+        <v>0.34253048896789551</v>
       </c>
       <c r="DC9" s="0">
-        <v>0.34800851345062256</v>
+        <v>0.34856051206588745</v>
       </c>
       <c r="DD9" s="0">
-        <v>0.3000761866569519</v>
+        <v>0.2901061475276947</v>
       </c>
       <c r="DE9" s="0">
-        <v>0.24734130501747131</v>
+        <v>0.26080074906349182</v>
       </c>
       <c r="DF9" s="0">
-        <v>0.37374278903007507</v>
+        <v>0.35395759344100952</v>
       </c>
       <c r="DG9" s="0">
-        <v>0.33320862054824829</v>
+        <v>0.36359825730323792</v>
       </c>
       <c r="DH9" s="0">
-        <v>0.38210216164588928</v>
+        <v>0.389658123254776</v>
       </c>
       <c r="DI9" s="0">
-        <v>0.36989274621009827</v>
+        <v>0.35907894372940064</v>
       </c>
       <c r="DJ9" s="0">
-        <v>0.26575437188148499</v>
+        <v>0.33348885178565979</v>
       </c>
       <c r="DK9" s="0">
-        <v>0.35724151134490967</v>
+        <v>0.3738349974155426</v>
       </c>
       <c r="DL9" s="0">
-        <v>0.21086382865905762</v>
+        <v>0.26215773820877075</v>
       </c>
       <c r="DM9" s="0">
-        <v>0.35739949345588684</v>
+        <v>0.33063474297523499</v>
       </c>
       <c r="DN9" s="0">
-        <v>0.42362922430038452</v>
+        <v>0.4003385603427887</v>
       </c>
       <c r="DO9" s="0">
-        <v>0.35860958695411682</v>
+        <v>0.33356213569641113</v>
       </c>
       <c r="DP9" s="0">
-        <v>0.27123865485191345</v>
+        <v>0.28910505771636963</v>
       </c>
       <c r="DQ9" s="0">
-        <v>0.34921526908874512</v>
+        <v>0.29622319340705872</v>
       </c>
       <c r="DR9" s="0">
-        <v>0.29151821136474609</v>
+        <v>0.24256278574466705</v>
       </c>
       <c r="DS9" s="0">
-        <v>0.25239035487174988</v>
+        <v>0.35207438468933106</v>
       </c>
     </row>
     <row r="10">
@@ -3995,364 +3996,364 @@
         <v>31</v>
       </c>
       <c r="D10" s="0">
-        <v>0.28066214919090271</v>
+        <v>0.42451149225234985</v>
       </c>
       <c r="E10" s="0">
-        <v>0.28874638676643372</v>
+        <v>0.41385757923126221</v>
       </c>
       <c r="F10" s="0">
-        <v>0.27530491352081299</v>
+        <v>0.41149094700813293</v>
       </c>
       <c r="G10" s="0">
-        <v>0.27386307716369629</v>
+        <v>0.3988879919052124</v>
       </c>
       <c r="H10" s="0">
-        <v>0.24750836193561554</v>
+        <v>0.39438065886497498</v>
       </c>
       <c r="I10" s="0">
-        <v>0.27010351419448853</v>
+        <v>0.41486853361129761</v>
       </c>
       <c r="J10" s="0">
-        <v>0.26536202430725098</v>
+        <v>0.38152742385864258</v>
       </c>
       <c r="K10" s="0">
-        <v>0.26643964648246765</v>
+        <v>0.39151304960250854</v>
       </c>
       <c r="L10" s="0">
-        <v>0.28363162279129028</v>
+        <v>0.41465556621551514</v>
       </c>
       <c r="M10" s="0">
-        <v>0.27187544107437134</v>
+        <v>0.40143373608589172</v>
       </c>
       <c r="N10" s="0">
-        <v>0.35464397072792053</v>
+        <v>0.46699324250221253</v>
       </c>
       <c r="O10" s="0">
-        <v>0.32896485924720764</v>
+        <v>0.44834989309310913</v>
       </c>
       <c r="P10" s="0">
-        <v>0.24694184958934784</v>
+        <v>0.38735249638557434</v>
       </c>
       <c r="Q10" s="0">
-        <v>0.28794199228286743</v>
+        <v>0.4080108106136322</v>
       </c>
       <c r="R10" s="0">
-        <v>0.30100482702255249</v>
+        <v>0.4662092924118042</v>
       </c>
       <c r="S10" s="0">
-        <v>0.33328917622566223</v>
+        <v>0.46801191568374634</v>
       </c>
       <c r="T10" s="0">
-        <v>0.23584003746509552</v>
+        <v>0.37787830829620361</v>
       </c>
       <c r="U10" s="0">
-        <v>0.25534108281135559</v>
+        <v>0.36943849921226502</v>
       </c>
       <c r="V10" s="0">
-        <v>0.32018387317657471</v>
+        <v>0.45238849520683289</v>
       </c>
       <c r="W10" s="0">
-        <v>0.27582329511642456</v>
+        <v>0.40778994560241699</v>
       </c>
       <c r="X10" s="0">
-        <v>0.30939310789108276</v>
+        <v>0.36270865797996521</v>
       </c>
       <c r="Y10" s="0">
-        <v>0.30472207069396973</v>
+        <v>0.41264611482620239</v>
       </c>
       <c r="Z10" s="0">
-        <v>0.3264293372631073</v>
+        <v>0.31670567393302918</v>
       </c>
       <c r="AA10" s="0">
-        <v>0.3168891966342926</v>
+        <v>0.31030210852622986</v>
       </c>
       <c r="AB10" s="0">
-        <v>0.36123329401016235</v>
+        <v>0.37578257918357849</v>
       </c>
       <c r="AC10" s="0">
-        <v>0.33964574337005615</v>
+        <v>0.34693211317062378</v>
       </c>
       <c r="AD10" s="0">
-        <v>0.27855411171913147</v>
+        <v>0.31852748990058899</v>
       </c>
       <c r="AE10" s="0">
-        <v>0.32645028829574585</v>
+        <v>0.3330632746219635</v>
       </c>
       <c r="AF10" s="0">
-        <v>0.28006887435913086</v>
+        <v>0.35865238308906555</v>
       </c>
       <c r="AG10" s="0">
-        <v>0.2880101203918457</v>
+        <v>0.30722692608833313</v>
       </c>
       <c r="AH10" s="0">
-        <v>0.3264167308807373</v>
+        <v>0.44804507493972778</v>
       </c>
       <c r="AI10" s="0">
-        <v>0.26767176389694214</v>
+        <v>0.35885891318321228</v>
       </c>
       <c r="AJ10" s="0">
-        <v>0.34032273292541504</v>
+        <v>0.35369491577148438</v>
       </c>
       <c r="AK10" s="0">
-        <v>0.26937410235404968</v>
+        <v>0.31968483328819275</v>
       </c>
       <c r="AL10" s="0">
-        <v>0.3081815242767334</v>
+        <v>0.40759918093681336</v>
       </c>
       <c r="AM10" s="0">
-        <v>0.2569831907749176</v>
+        <v>0.367696613073349</v>
       </c>
       <c r="AN10" s="0">
-        <v>0.32915735244750977</v>
+        <v>0.3416740894317627</v>
       </c>
       <c r="AO10" s="0">
-        <v>0.35701483488082886</v>
+        <v>0.34901887178421021</v>
       </c>
       <c r="AP10" s="0">
-        <v>0.25722825527191162</v>
+        <v>0.37929457426071167</v>
       </c>
       <c r="AQ10" s="0">
-        <v>0.28100383281707764</v>
+        <v>0.31982710957527161</v>
       </c>
       <c r="AR10" s="0">
-        <v>0.32832950353622437</v>
+        <v>0.37457156181335449</v>
       </c>
       <c r="AS10" s="0">
-        <v>0.29405248165130615</v>
+        <v>0.3702748715877533</v>
       </c>
       <c r="AT10" s="0">
-        <v>0.29758438467979431</v>
+        <v>0.40005296468734741</v>
       </c>
       <c r="AU10" s="0">
-        <v>0.29138320684432983</v>
+        <v>0.30706110596656799</v>
       </c>
       <c r="AV10" s="0">
-        <v>0.25927034020423889</v>
+        <v>0.34956154227256775</v>
       </c>
       <c r="AW10" s="0">
-        <v>0.29147598147392273</v>
+        <v>0.38363215327262879</v>
       </c>
       <c r="AX10" s="0">
-        <v>0.33022642135620117</v>
+        <v>0.3564603328704834</v>
       </c>
       <c r="AY10" s="0">
-        <v>0.32221066951751709</v>
+        <v>0.33543729782104492</v>
       </c>
       <c r="AZ10" s="0">
-        <v>0.3234398365020752</v>
+        <v>0.35528892278671265</v>
       </c>
       <c r="BA10" s="0">
-        <v>0.29362887144088745</v>
+        <v>0.32782441377639771</v>
       </c>
       <c r="BB10" s="0">
-        <v>0.30512499809265137</v>
+        <v>0.36828950047492981</v>
       </c>
       <c r="BC10" s="0">
-        <v>0.33145371079444885</v>
+        <v>0.33950179815292358</v>
       </c>
       <c r="BD10" s="0">
-        <v>0.27673953771591187</v>
+        <v>0.30625501275062561</v>
       </c>
       <c r="BE10" s="0">
-        <v>0.25949710607528687</v>
+        <v>0.3482966423034668</v>
       </c>
       <c r="BF10" s="0">
-        <v>0.37481039762496948</v>
+        <v>0.38931500911712646</v>
       </c>
       <c r="BG10" s="0">
-        <v>0.31498211622238159</v>
+        <v>0.34988757967948914</v>
       </c>
       <c r="BH10" s="0">
-        <v>0.33122873306274414</v>
+        <v>0.35500338673591614</v>
       </c>
       <c r="BI10" s="0">
-        <v>0.29680708050727844</v>
+        <v>0.35432487726211548</v>
       </c>
       <c r="BJ10" s="0">
-        <v>0.25955605506896973</v>
+        <v>0.37501227855682373</v>
       </c>
       <c r="BK10" s="0">
-        <v>0.31633186340332031</v>
+        <v>0.33678087592124939</v>
       </c>
       <c r="BL10" s="0">
-        <v>0.28110587596893311</v>
+        <v>0.39608818292617798</v>
       </c>
       <c r="BM10" s="0">
-        <v>0.3505895733833313</v>
+        <v>0.38575887680053711</v>
       </c>
       <c r="BN10" s="0">
-        <v>0.30834490060806274</v>
+        <v>0.41843658685684204</v>
       </c>
       <c r="BO10" s="0">
-        <v>0.31473422050476074</v>
+        <v>0.35500562191009522</v>
       </c>
       <c r="BP10" s="0">
-        <v>0.28282436728477478</v>
+        <v>0.35526522994041443</v>
       </c>
       <c r="BQ10" s="0">
-        <v>0.31221038103103638</v>
+        <v>0.37969532608985901</v>
       </c>
       <c r="BR10" s="0">
-        <v>0.31985360383987427</v>
+        <v>0.36860817670822144</v>
       </c>
       <c r="BS10" s="0">
-        <v>0.33409735560417175</v>
+        <v>0.37034901976585388</v>
       </c>
       <c r="BT10" s="0">
-        <v>0.30347567796707153</v>
+        <v>0.37520191073417664</v>
       </c>
       <c r="BU10" s="0">
-        <v>0.34364208579063416</v>
+        <v>0.36380863189697266</v>
       </c>
       <c r="BV10" s="0">
-        <v>0.34715870022773743</v>
+        <v>0.40866068005561829</v>
       </c>
       <c r="BW10" s="0">
-        <v>0.3632473349571228</v>
+        <v>0.3428141176700592</v>
       </c>
       <c r="BX10" s="0">
-        <v>0.36767038702964783</v>
+        <v>0.3465273380279541</v>
       </c>
       <c r="BY10" s="0">
-        <v>0.37809735536575317</v>
+        <v>0.43456530570983887</v>
       </c>
       <c r="BZ10" s="0">
-        <v>0.33047002553939819</v>
+        <v>0.4126322865486145</v>
       </c>
       <c r="CA10" s="0">
-        <v>0.32975497841835022</v>
+        <v>0.3409670889377594</v>
       </c>
       <c r="CB10" s="0">
-        <v>0.39853322505950928</v>
+        <v>0.4095579981803894</v>
       </c>
       <c r="CC10" s="0">
-        <v>0.37685444951057434</v>
+        <v>0.38737699389457703</v>
       </c>
       <c r="CD10" s="0">
-        <v>0.2945483922958374</v>
+        <v>0.33461236953735352</v>
       </c>
       <c r="CE10" s="0">
-        <v>0.32154473662376404</v>
+        <v>0.35315519571304321</v>
       </c>
       <c r="CF10" s="0">
-        <v>0.40373870730400085</v>
+        <v>0.41103288531303406</v>
       </c>
       <c r="CG10" s="0">
-        <v>0.2530207633972168</v>
+        <v>0.36200562119483948</v>
       </c>
       <c r="CH10" s="0">
-        <v>0.21987873315811157</v>
+        <v>0.29430285096168518</v>
       </c>
       <c r="CI10" s="0">
-        <v>0.29763472080230713</v>
+        <v>0.33674386143684387</v>
       </c>
       <c r="CJ10" s="0">
-        <v>0.32410609722137451</v>
+        <v>0.37319982051849365</v>
       </c>
       <c r="CK10" s="0">
-        <v>0.36049431562423706</v>
+        <v>0.37431815266609192</v>
       </c>
       <c r="CL10" s="0">
-        <v>0.38834965229034424</v>
+        <v>0.32138130068778992</v>
       </c>
       <c r="CM10" s="0">
-        <v>0.30748492479324341</v>
+        <v>0.38202530145645142</v>
       </c>
       <c r="CN10" s="0">
-        <v>0.36930254101753235</v>
+        <v>0.3865104615688324</v>
       </c>
       <c r="CO10" s="0">
-        <v>0.32964885234832764</v>
+        <v>0.44084820151329041</v>
       </c>
       <c r="CP10" s="0">
-        <v>0.33601453900337219</v>
+        <v>0.3567768931388855</v>
       </c>
       <c r="CQ10" s="0">
-        <v>0.36382061243057251</v>
+        <v>0.34239092469215393</v>
       </c>
       <c r="CR10" s="0">
-        <v>0.33824130892753601</v>
+        <v>0.38044333457946777</v>
       </c>
       <c r="CS10" s="0">
-        <v>0.25962892174720764</v>
+        <v>0.40322542190551758</v>
       </c>
       <c r="CT10" s="0">
-        <v>0.30793130397796631</v>
+        <v>0.36209923028945923</v>
       </c>
       <c r="CU10" s="0">
-        <v>0.25149637460708618</v>
+        <v>0.32858613133430481</v>
       </c>
       <c r="CV10" s="0">
-        <v>0.32582524418830872</v>
+        <v>0.37411698698997498</v>
       </c>
       <c r="CW10" s="0">
-        <v>0.33573028445243835</v>
+        <v>0.41077056527137756</v>
       </c>
       <c r="CX10" s="0">
-        <v>0.27668237686157227</v>
+        <v>0.33442828059196472</v>
       </c>
       <c r="CY10" s="0">
-        <v>0.23383021354675293</v>
+        <v>0.2994752824306488</v>
       </c>
       <c r="CZ10" s="0">
-        <v>0.28646326065063477</v>
+        <v>0.38948878645896912</v>
       </c>
       <c r="DA10" s="0">
-        <v>0.28849729895591736</v>
+        <v>0.33288103342056275</v>
       </c>
       <c r="DB10" s="0">
-        <v>0.2743147611618042</v>
+        <v>0.32141435146331787</v>
       </c>
       <c r="DC10" s="0">
-        <v>0.30962270498275757</v>
+        <v>0.34408834576606751</v>
       </c>
       <c r="DD10" s="0">
-        <v>0.26844748854637146</v>
+        <v>0.3225860595703125</v>
       </c>
       <c r="DE10" s="0">
-        <v>0.22071182727813721</v>
+        <v>0.32495352625846863</v>
       </c>
       <c r="DF10" s="0">
-        <v>0.36316651105880737</v>
+        <v>0.36277005076408386</v>
       </c>
       <c r="DG10" s="0">
-        <v>0.33337202668190002</v>
+        <v>0.34367302060127258</v>
       </c>
       <c r="DH10" s="0">
-        <v>0.32268431782722473</v>
+        <v>0.40334975719451904</v>
       </c>
       <c r="DI10" s="0">
-        <v>0.35157784819602966</v>
+        <v>0.3392917811870575</v>
       </c>
       <c r="DJ10" s="0">
-        <v>0.28454744815826416</v>
+        <v>0.34046509861946106</v>
       </c>
       <c r="DK10" s="0">
-        <v>0.32252880930900574</v>
+        <v>0.33981841802597046</v>
       </c>
       <c r="DL10" s="0">
-        <v>0.24488939344882965</v>
+        <v>0.26385357975959778</v>
       </c>
       <c r="DM10" s="0">
-        <v>0.31271001696586609</v>
+        <v>0.32016214728355408</v>
       </c>
       <c r="DN10" s="0">
-        <v>0.36105680465698242</v>
+        <v>0.40590345859527588</v>
       </c>
       <c r="DO10" s="0">
-        <v>0.32397586107254028</v>
+        <v>0.43918737769126892</v>
       </c>
       <c r="DP10" s="0">
-        <v>0.24198167026042938</v>
+        <v>0.31524562835693359</v>
       </c>
       <c r="DQ10" s="0">
-        <v>0.34613382816314697</v>
+        <v>0.33421838283538818</v>
       </c>
       <c r="DR10" s="0">
-        <v>0.27232784032821655</v>
+        <v>0.26957184076309204</v>
       </c>
       <c r="DS10" s="0">
-        <v>0.29775971174240112</v>
+        <v>0.32814544439315796</v>
       </c>
     </row>
     <row r="11">
@@ -4366,364 +4367,364 @@
         <v>32</v>
       </c>
       <c r="D11" s="0">
-        <v>0.32294544577598572</v>
+        <v>0.3012942373752594</v>
       </c>
       <c r="E11" s="0">
-        <v>0.31406664848327637</v>
+        <v>0.2930220365524292</v>
       </c>
       <c r="F11" s="0">
-        <v>0.32445308566093445</v>
+        <v>0.29558280110359192</v>
       </c>
       <c r="G11" s="0">
-        <v>0.32427242398262024</v>
+        <v>0.29443192481994629</v>
       </c>
       <c r="H11" s="0">
-        <v>0.30307120084762573</v>
+        <v>0.24929507076740265</v>
       </c>
       <c r="I11" s="0">
-        <v>0.32572218775749207</v>
+        <v>0.26209121942520142</v>
       </c>
       <c r="J11" s="0">
-        <v>0.30472391843795776</v>
+        <v>0.26051780581474304</v>
       </c>
       <c r="K11" s="0">
-        <v>0.31420338153839111</v>
+        <v>0.2578175961971283</v>
       </c>
       <c r="L11" s="0">
-        <v>0.32237124443054199</v>
+        <v>0.3011532723903656</v>
       </c>
       <c r="M11" s="0">
-        <v>0.30461755394935608</v>
+        <v>0.26008960604667664</v>
       </c>
       <c r="N11" s="0">
-        <v>0.40849539637565613</v>
+        <v>0.35151445865631104</v>
       </c>
       <c r="O11" s="0">
-        <v>0.35399633646011353</v>
+        <v>0.31460347771644592</v>
       </c>
       <c r="P11" s="0">
-        <v>0.27959629893302917</v>
+        <v>0.26304686069488525</v>
       </c>
       <c r="Q11" s="0">
-        <v>0.31504091620445251</v>
+        <v>0.29741010069847107</v>
       </c>
       <c r="R11" s="0">
-        <v>0.33734181523323059</v>
+        <v>0.33337751030921936</v>
       </c>
       <c r="S11" s="0">
-        <v>0.36818793416023254</v>
+        <v>0.33082675933837891</v>
       </c>
       <c r="T11" s="0">
-        <v>0.27342870831489563</v>
+        <v>0.25049892067909241</v>
       </c>
       <c r="U11" s="0">
-        <v>0.27662521600723267</v>
+        <v>0.23935315012931824</v>
       </c>
       <c r="V11" s="0">
-        <v>0.34279575943946838</v>
+        <v>0.30974769592285156</v>
       </c>
       <c r="W11" s="0">
-        <v>0.32742536067962646</v>
+        <v>0.28073182702064514</v>
       </c>
       <c r="X11" s="0">
-        <v>0.3492247462272644</v>
+        <v>0.39169770479202271</v>
       </c>
       <c r="Y11" s="0">
-        <v>0.34295016527175903</v>
+        <v>0.41701668500900269</v>
       </c>
       <c r="Z11" s="0">
-        <v>0.27420893311500549</v>
+        <v>0.38724878430366516</v>
       </c>
       <c r="AA11" s="0">
-        <v>0.37099730968475342</v>
+        <v>0.36109116673469543</v>
       </c>
       <c r="AB11" s="0">
-        <v>0.32363271713256836</v>
+        <v>0.3849775493144989</v>
       </c>
       <c r="AC11" s="0">
-        <v>0.34502840042114258</v>
+        <v>0.42280322313308716</v>
       </c>
       <c r="AD11" s="0">
-        <v>0.3394000232219696</v>
+        <v>0.39528760313987732</v>
       </c>
       <c r="AE11" s="0">
-        <v>0.31641533970832825</v>
+        <v>0.35611236095428467</v>
       </c>
       <c r="AF11" s="0">
-        <v>0.25798219442367554</v>
+        <v>0.36163344979286194</v>
       </c>
       <c r="AG11" s="0">
-        <v>0.27877923846244812</v>
+        <v>0.35706746578216553</v>
       </c>
       <c r="AH11" s="0">
-        <v>0.37691012024879456</v>
+        <v>0.40143793821334839</v>
       </c>
       <c r="AI11" s="0">
-        <v>0.30550247430801392</v>
+        <v>0.38846161961555481</v>
       </c>
       <c r="AJ11" s="0">
-        <v>0.2865578830242157</v>
+        <v>0.4046606719493866</v>
       </c>
       <c r="AK11" s="0">
-        <v>0.32133865356445312</v>
+        <v>0.36615735292434692</v>
       </c>
       <c r="AL11" s="0">
-        <v>0.3022899329662323</v>
+        <v>0.38429871201515198</v>
       </c>
       <c r="AM11" s="0">
-        <v>0.26191487908363342</v>
+        <v>0.38211613893508911</v>
       </c>
       <c r="AN11" s="0">
-        <v>0.32906496524810791</v>
+        <v>0.43093860149383545</v>
       </c>
       <c r="AO11" s="0">
-        <v>0.33172458410263062</v>
+        <v>0.37456387281417847</v>
       </c>
       <c r="AP11" s="0">
-        <v>0.32708922028541565</v>
+        <v>0.31594541668891907</v>
       </c>
       <c r="AQ11" s="0">
-        <v>0.30982962250709534</v>
+        <v>0.36219343543052673</v>
       </c>
       <c r="AR11" s="0">
-        <v>0.30907842516899109</v>
+        <v>0.3297065794467926</v>
       </c>
       <c r="AS11" s="0">
-        <v>0.32173621654510498</v>
+        <v>0.33677783608436584</v>
       </c>
       <c r="AT11" s="0">
-        <v>0.34268200397491455</v>
+        <v>0.37007519602775574</v>
       </c>
       <c r="AU11" s="0">
-        <v>0.33540400862693787</v>
+        <v>0.35800886154174805</v>
       </c>
       <c r="AV11" s="0">
-        <v>0.28413644433021545</v>
+        <v>0.37744554877281189</v>
       </c>
       <c r="AW11" s="0">
-        <v>0.29488840699195862</v>
+        <v>0.33650478720664978</v>
       </c>
       <c r="AX11" s="0">
-        <v>0.40252572298049927</v>
+        <v>0.37026071548461914</v>
       </c>
       <c r="AY11" s="0">
-        <v>0.29862517118453979</v>
+        <v>0.41064390540122986</v>
       </c>
       <c r="AZ11" s="0">
-        <v>0.34272536635398865</v>
+        <v>0.45327234268188477</v>
       </c>
       <c r="BA11" s="0">
-        <v>0.32998636364936829</v>
+        <v>0.40939879417419434</v>
       </c>
       <c r="BB11" s="0">
-        <v>0.31032028794288635</v>
+        <v>0.38349318504333496</v>
       </c>
       <c r="BC11" s="0">
-        <v>0.29401364922523499</v>
+        <v>0.41469594836235046</v>
       </c>
       <c r="BD11" s="0">
-        <v>0.27805793285369873</v>
+        <v>0.32921499013900757</v>
       </c>
       <c r="BE11" s="0">
-        <v>0.34619060158729553</v>
+        <v>0.40179309248924255</v>
       </c>
       <c r="BF11" s="0">
-        <v>0.35000506043434143</v>
+        <v>0.34065777063369751</v>
       </c>
       <c r="BG11" s="0">
-        <v>0.28172236680984497</v>
+        <v>0.36257860064506531</v>
       </c>
       <c r="BH11" s="0">
-        <v>0.33695480227470398</v>
+        <v>0.37040156126022339</v>
       </c>
       <c r="BI11" s="0">
-        <v>0.32750624418258667</v>
+        <v>0.36310279369354248</v>
       </c>
       <c r="BJ11" s="0">
-        <v>0.28209066390991211</v>
+        <v>0.32645693421363831</v>
       </c>
       <c r="BK11" s="0">
-        <v>0.28195315599441528</v>
+        <v>0.35921925306320191</v>
       </c>
       <c r="BL11" s="0">
-        <v>0.32154318690299988</v>
+        <v>0.42763221263885498</v>
       </c>
       <c r="BM11" s="0">
-        <v>0.29409858584403992</v>
+        <v>0.44181454181671143</v>
       </c>
       <c r="BN11" s="0">
-        <v>0.32897990942001343</v>
+        <v>0.39141800999641419</v>
       </c>
       <c r="BO11" s="0">
-        <v>0.31081226468086243</v>
+        <v>0.43093571066856384</v>
       </c>
       <c r="BP11" s="0">
-        <v>0.32182151079177856</v>
+        <v>0.31353604793548584</v>
       </c>
       <c r="BQ11" s="0">
-        <v>0.31860533356666565</v>
+        <v>0.41853964328765869</v>
       </c>
       <c r="BR11" s="0">
-        <v>0.29280802607536316</v>
+        <v>0.38696214556694031</v>
       </c>
       <c r="BS11" s="0">
-        <v>0.34015342593193054</v>
+        <v>0.36846321821212769</v>
       </c>
       <c r="BT11" s="0">
-        <v>0.27123269438743591</v>
+        <v>0.38088482618331909</v>
       </c>
       <c r="BU11" s="0">
-        <v>0.3008708655834198</v>
+        <v>0.36526796221733093</v>
       </c>
       <c r="BV11" s="0">
-        <v>0.41210746765136719</v>
+        <v>0.38512074947357178</v>
       </c>
       <c r="BW11" s="0">
-        <v>0.35815459489822388</v>
+        <v>0.3722957968711853</v>
       </c>
       <c r="BX11" s="0">
-        <v>0.39178666472434998</v>
+        <v>0.42161768674850464</v>
       </c>
       <c r="BY11" s="0">
-        <v>0.36968567967414856</v>
+        <v>0.40048888325691223</v>
       </c>
       <c r="BZ11" s="0">
-        <v>0.33950838446617126</v>
+        <v>0.41051658987998963</v>
       </c>
       <c r="CA11" s="0">
-        <v>0.32146838307380676</v>
+        <v>0.4037553071975708</v>
       </c>
       <c r="CB11" s="0">
-        <v>0.35975876450538635</v>
+        <v>0.45789569616317749</v>
       </c>
       <c r="CC11" s="0">
-        <v>0.37012052536010742</v>
+        <v>0.44490593671798706</v>
       </c>
       <c r="CD11" s="0">
-        <v>0.28292924165725708</v>
+        <v>0.39443486928939819</v>
       </c>
       <c r="CE11" s="0">
-        <v>0.34702363610267639</v>
+        <v>0.41555842757225037</v>
       </c>
       <c r="CF11" s="0">
-        <v>0.28031402826309204</v>
+        <v>0.34521621465682983</v>
       </c>
       <c r="CG11" s="0">
-        <v>0.33574181795120239</v>
+        <v>0.41915386915206909</v>
       </c>
       <c r="CH11" s="0">
-        <v>0.27862176299095154</v>
+        <v>0.28033718466758728</v>
       </c>
       <c r="CI11" s="0">
-        <v>0.26651003956794739</v>
+        <v>0.38371577858924866</v>
       </c>
       <c r="CJ11" s="0">
-        <v>0.34497156739234924</v>
+        <v>0.38313865661621094</v>
       </c>
       <c r="CK11" s="0">
-        <v>0.36801540851593018</v>
+        <v>0.43050616979598999</v>
       </c>
       <c r="CL11" s="0">
-        <v>0.37286704778671265</v>
+        <v>0.44444847106933594</v>
       </c>
       <c r="CM11" s="0">
-        <v>0.35436001420021057</v>
+        <v>0.35216251015663147</v>
       </c>
       <c r="CN11" s="0">
-        <v>0.37472814321517944</v>
+        <v>0.36581245064735413</v>
       </c>
       <c r="CO11" s="0">
-        <v>0.33736446499824524</v>
+        <v>0.427482008934021</v>
       </c>
       <c r="CP11" s="0">
-        <v>0.34644854068756104</v>
+        <v>0.39122357964515686</v>
       </c>
       <c r="CQ11" s="0">
-        <v>0.35039642453193665</v>
+        <v>0.40012189745903015</v>
       </c>
       <c r="CR11" s="0">
-        <v>0.366201251745224</v>
+        <v>0.4358045756816864</v>
       </c>
       <c r="CS11" s="0">
-        <v>0.32330763339996338</v>
+        <v>0.38156062364578247</v>
       </c>
       <c r="CT11" s="0">
-        <v>0.41613316535949707</v>
+        <v>0.4145086407661438</v>
       </c>
       <c r="CU11" s="0">
-        <v>0.39046370983123779</v>
+        <v>0.35570999979972839</v>
       </c>
       <c r="CV11" s="0">
-        <v>0.34623280167579651</v>
+        <v>0.30639547109603882</v>
       </c>
       <c r="CW11" s="0">
-        <v>0.29344218969345093</v>
+        <v>0.40682697296142578</v>
       </c>
       <c r="CX11" s="0">
-        <v>0.25342297554016113</v>
+        <v>0.28193002939224243</v>
       </c>
       <c r="CY11" s="0">
-        <v>0.2999328076839447</v>
+        <v>0.36474215984344482</v>
       </c>
       <c r="CZ11" s="0">
-        <v>0.29920908808708191</v>
+        <v>0.38730773329734802</v>
       </c>
       <c r="DA11" s="0">
-        <v>0.31282985210418701</v>
+        <v>0.37781587243080139</v>
       </c>
       <c r="DB11" s="0">
-        <v>0.37977617979049683</v>
+        <v>0.46879324316978455</v>
       </c>
       <c r="DC11" s="0">
-        <v>0.35440570116043091</v>
+        <v>0.37008032202720642</v>
       </c>
       <c r="DD11" s="0">
-        <v>0.30069535970687866</v>
+        <v>0.37600451707839966</v>
       </c>
       <c r="DE11" s="0">
-        <v>0.25779128074645996</v>
+        <v>0.3060881495475769</v>
       </c>
       <c r="DF11" s="0">
-        <v>0.33634376525878906</v>
+        <v>0.44891205430030823</v>
       </c>
       <c r="DG11" s="0">
-        <v>0.33127650618553162</v>
+        <v>0.40788280963897705</v>
       </c>
       <c r="DH11" s="0">
-        <v>0.35146504640579224</v>
+        <v>0.40555009245872498</v>
       </c>
       <c r="DI11" s="0">
-        <v>0.33688661456108093</v>
+        <v>0.40358126163482666</v>
       </c>
       <c r="DJ11" s="0">
-        <v>0.36058890819549561</v>
+        <v>0.42316707968711853</v>
       </c>
       <c r="DK11" s="0">
-        <v>0.28826376795768738</v>
+        <v>0.35000154376029968</v>
       </c>
       <c r="DL11" s="0">
-        <v>0.20165997743606567</v>
+        <v>0.33009263873100281</v>
       </c>
       <c r="DM11" s="0">
-        <v>0.3407742977142334</v>
+        <v>0.36846309900283814</v>
       </c>
       <c r="DN11" s="0">
-        <v>0.41795918345451355</v>
+        <v>0.43995815515518189</v>
       </c>
       <c r="DO11" s="0">
-        <v>0.33459421992301941</v>
+        <v>0.44310343265533447</v>
       </c>
       <c r="DP11" s="0">
-        <v>0.29739844799041748</v>
+        <v>0.34326449036598206</v>
       </c>
       <c r="DQ11" s="0">
-        <v>0.27449575066566467</v>
+        <v>0.39468842744827271</v>
       </c>
       <c r="DR11" s="0">
-        <v>0.30111721158027649</v>
+        <v>0.3319179117679596</v>
       </c>
       <c r="DS11" s="0">
-        <v>0.32249024510383606</v>
+        <v>0.34982827305793762</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_gmprob.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/group_roi_means_gmprob.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
